--- a/Benchmark/UrlManual_normalized.xlsx
+++ b/Benchmark/UrlManual_normalized.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:C545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,11 @@
           <t>url</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>es_dataset</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -451,6 +456,9 @@
           <t>https://www.kaggle.com/ruizgara/socofing</t>
         </is>
       </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,6 +471,9 @@
           <t>https://www.kaggle.com/datasets/ipateam/nuinsseg</t>
         </is>
       </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -472,8 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.github.com/masih4/NuInsSeg</t>
-        </is>
+          <t>https://github.com/masih4/NuInsSeg</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -487,6 +501,9 @@
           <t>https://www.tissuegnostics.com/</t>
         </is>
       </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,8 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41374-020-00514-0</t>
-        </is>
+          <t>https://doi.org/10.1038/s41374-020-00514-0</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -508,8 +528,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s00412-016-0614-5</t>
-        </is>
+          <t>https://doi.org/10.1007/s00412-016-0614-5</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -520,8 +543,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1177/1066896913517939</t>
-        </is>
+          <t>https://doi.org/10.1177/1066896913517939</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -532,8 +558,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2017.2677499</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2017.2677499</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -544,8 +573,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.compbiomed.2021.104349</t>
-        </is>
+          <t>https://doi.org/10.1016/j.compbiomed.2021.104349</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -556,8 +588,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.media.2019.101563</t>
-        </is>
+          <t>https://doi.org/10.1016/j.media.2019.101563</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -568,8 +603,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2019.2947628</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2019.2947628</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -580,8 +618,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2018.2865709</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2018.2865709</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -592,8 +633,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/ISBI.2017.7950669</t>
-        </is>
+          <t>https://doi.org/10.1109/ISBI.2017.7950669</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -604,8 +648,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.media.2020.101786</t>
-        </is>
+          <t>https://doi.org/10.1016/j.media.2020.101771</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -616,8 +663,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3389/fmed.2022.978146</t>
-        </is>
+          <t>https://doi.org/10.3389/fmed.2022.978146</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -628,8 +678,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2018.2842767</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2018.2842767</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -640,8 +693,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-020-00608-w</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-020-00608-w</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -652,8 +708,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/diagnostics11060967</t>
-        </is>
+          <t>https://doi.org/10.3390/diagnostics11060967</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -664,8 +723,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2021.3085712</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2021.3085712</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -676,8 +738,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/978-3-030-23937-4_2</t>
-        </is>
+          <t>https://doi.org/10.1007/978-3-030-23937-4_9</t>
+        </is>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -688,8 +753,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-020-0528-1</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-020-0528-1</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -700,8 +768,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3389/fbioe.2019.00053</t>
-        </is>
+          <t>https://doi.org/10.3389/fbioe.2019.00053</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -712,8 +783,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2016.2525803</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2016.2525803</t>
+        </is>
+      </c>
+      <c r="C24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -724,8 +798,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.4103/2153-3539.186902</t>
-        </is>
+          <t>https://doi.org/10.4103/2153-3539.186902</t>
+        </is>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -736,8 +813,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1142/9789814644730_0029</t>
-        </is>
+          <t>https://doi.org/10.1142/9789814644730_0029</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -748,8 +828,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1091/mbc.E20-02-0156</t>
-        </is>
+          <t>https://doi.org/10.1091/mbc.E20-02-0156</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -760,8 +843,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2022.3157048</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2022.3157048</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -772,8 +858,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/978-3-319-24574-4_28</t>
-        </is>
+          <t>https://doi.org/10.1007/978-3-319-24574-4_28</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -784,8 +873,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/CVPR.2016.90</t>
-        </is>
+          <t>https://doi.org/10.1109/CVPR.2016.90</t>
+        </is>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -796,8 +888,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TMI.2022.3156023</t>
-        </is>
+          <t>https://doi.org/10.1109/TMI.2022.3156023</t>
+        </is>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -808,8 +903,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/978-3-030-68763-2_26</t>
-        </is>
+          <t>https://doi.org/10.1007/978-3-030-68763-2_26</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -823,6 +921,9 @@
           <t>https://www.kaggle.com/datasets/nutritionverse/nutritionverse-real</t>
         </is>
       </c>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -835,6 +936,9 @@
           <t>https://www.kaggle.com/datasets/vinnyr12/eye-movements</t>
         </is>
       </c>
+      <c r="C34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -844,8 +948,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.anonymous.4open.science/r/tabpfn-ood-4E65</t>
-        </is>
+          <t>https://anonymous.4open.science/r/tabpfn-ood-4E65</t>
+        </is>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -856,8 +963,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.archive.ics.uci.edu/ml/datasets/Contraceptive+Method+Choice</t>
-        </is>
+          <t>https://archive.ics.uci.edu/ml/datasets/Contraceptive+Method+Choice</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -868,8 +978,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.archive.ics.uci.edu/dataset/186/wine+quality</t>
-        </is>
+          <t>https://archive.ics.uci.edu/dataset/186/wine+quality</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -880,8 +993,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.openml.org/search?id=31&amp;sort=runs&amp;status=active&amp;type=data</t>
-        </is>
+          <t>https://www.openml.org/search?id=45021&amp;status=active&amp;type=data</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -895,6 +1011,9 @@
           <t>https://www.kaggle.com/datasets/vstacknocopyright/electricity</t>
         </is>
       </c>
+      <c r="C39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -907,6 +1026,9 @@
           <t>https://www.kaggle.com/datasets/fedesoriano/heart-failure-prediction</t>
         </is>
       </c>
+      <c r="C40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -919,6 +1041,9 @@
           <t>https://www.kaggle.com/datasets/alexanderliapatis/miniboone</t>
         </is>
       </c>
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -931,6 +1056,9 @@
           <t>https://www.kaggle.com/datasets/uciml/iris</t>
         </is>
       </c>
+      <c r="C42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -943,6 +1071,9 @@
           <t>https://www.kaggle.com/datasets/youssefaboelwafa/clustering-penguins-species</t>
         </is>
       </c>
+      <c r="C43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -955,6 +1086,9 @@
           <t>https://www.kaggle.com/datasets/rodolfomendes/abalone-dataset</t>
         </is>
       </c>
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -967,6 +1101,9 @@
           <t>https://www.kaggle.com/datasets/abdullapathan/bikesharingdemand</t>
         </is>
       </c>
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -979,6 +1116,9 @@
           <t>https://www.kaggle.com/datasets/maajdl/yeh-concret-data</t>
         </is>
       </c>
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -991,6 +1131,9 @@
           <t>https://www.kaggle.com/datasets/owm4096/laptop-prices</t>
         </is>
       </c>
+      <c r="C47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1000,8 +1143,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.github.com/namkoong-lab/whyshift</t>
-        </is>
+          <t>https://github.com/namkoong-lab/whyshift</t>
+        </is>
+      </c>
+      <c r="C48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1012,8 +1158,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.github.com/blacksnail789521/Time-IMM</t>
-        </is>
+          <t>https://github.com/blacksnail789521/Time-IMM</t>
+        </is>
+      </c>
+      <c r="C49" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1024,8 +1173,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.github.com/blacksnail789521/IMM-TSF</t>
-        </is>
+          <t>https://github.com/blacksnail789521/IMM-TSF</t>
+        </is>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1039,6 +1191,9 @@
           <t>https://www.cs.ucr.edu/~eamonn/time_series_data_2018</t>
         </is>
       </c>
+      <c r="C51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1048,8 +1203,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.physionet.org/content/mimiciv/1.0</t>
-        </is>
+          <t>https://physionet.org/content/mimiciv/1.0</t>
+        </is>
+      </c>
+      <c r="C52" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1060,8 +1218,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.platform.openai.com/docs/models/gpt-4.1-nano</t>
-        </is>
+          <t>https://platform.openai.com/docs/models/gpt-4.1-nano</t>
+        </is>
+      </c>
+      <c r="C53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1072,8 +1233,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.archive.ics.uci.edu/dataset/321/electricityloaddiagrams20112014</t>
-        </is>
+          <t>https://archive.ics.uci.edu/dataset/321/electricityloaddiagrams20112014</t>
+        </is>
+      </c>
+      <c r="C54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1084,8 +1248,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.archive.physionet.org/challenge/2012</t>
-        </is>
+          <t>https://archive.physionet.org/challenge/2012</t>
+        </is>
+      </c>
+      <c r="C55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1099,6 +1266,9 @@
           <t>https://www.epa.gov/air-quality</t>
         </is>
       </c>
+      <c r="C56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1108,8 +1278,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.archive.ics.uci.edu/dataset/196/localization+data+for+person+activity</t>
-        </is>
+          <t>https://archive.ics.uci.edu/dataset/196/localization+data+for+person+activity</t>
+        </is>
+      </c>
+      <c r="C57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1120,8 +1293,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.data.gdeltproject.org/gdeltv2/masterfilelist.txt</t>
-        </is>
+          <t>http://data.gdeltproject.org/gdeltv2/masterfilelist.txt</t>
+        </is>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1132,8 +1308,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.physionet.org/content/mimiciv/3.1</t>
-        </is>
+          <t>https://physionet.org/content/mimiciv/3.1</t>
+        </is>
+      </c>
+      <c r="C59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1144,8 +1323,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.github.com/edebrouwer/gru_ode_bayes/tree/master/data_preproc/MIMIC</t>
-        </is>
+          <t>https://github.com/edebrouwer/gru_ode_bayes/tree/master/data_preproc/MIMIC</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1156,8 +1338,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.huggingface.co/datasets/Zihan1004/FNSPID</t>
-        </is>
+          <t>https://huggingface.co/datasets/Zihan1004/FNSPID</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1168,8 +1353,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.github.com/alibaba/clusterdata/tree/master</t>
-        </is>
+          <t>https://github.com/alibaba/clusterdata/tree/master?tab=readme-ov-file</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1180,8 +1368,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.aqs.epa.gov/aqsweb/airdata/download_files.html</t>
-        </is>
+          <t>https://aqs.epa.gov/aqsweb/airdata/download_files.html</t>
+        </is>
+      </c>
+      <c r="C63" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -1192,8 +1383,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.data.commoncrawl.org/crawl-data/CC-NEWS</t>
-        </is>
+          <t>https://data.commoncrawl.org/crawl-data/CC-NEWS</t>
+        </is>
+      </c>
+      <c r="C64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1204,8 +1398,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/blacksnail789521/time-imm</t>
-        </is>
+          <t>https://www.kaggle.com/datasets/blacksnail789521/time-imm/data</t>
+        </is>
+      </c>
+      <c r="C65" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1216,8 +1413,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.anonymous.4open.science/r/IMMTSF_NeurIPS2025</t>
-        </is>
+          <t>https://anonymous.4open.science/r/IMMTSF_NeurIPS2025</t>
+        </is>
+      </c>
+      <c r="C66" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1228,8 +1428,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.nips.cc/public/guides/CodeSubmissionPolicy</t>
-        </is>
+          <t>https://nips.cc/public/guides/CodeSubmissionPolicy</t>
+        </is>
+      </c>
+      <c r="C67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1240,8 +1443,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.neurips.cc/public/EthicsGuidelines</t>
-        </is>
+          <t>https://neurips.cc/public/EthicsGuidelines</t>
+        </is>
+      </c>
+      <c r="C68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1252,8 +1458,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.neurips.cc/Conferences/2025/LLM</t>
-        </is>
+          <t>https://neurips.cc/Conferences/2025/LLM</t>
+        </is>
+      </c>
+      <c r="C69" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1264,8 +1473,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15656471</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.15656471</t>
+        </is>
+      </c>
+      <c r="C70" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -1276,8 +1488,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.zenodo.org/communities/re-data/records</t>
-        </is>
+          <t>https://zenodo.org/communities/re-data/records</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1288,8 +1503,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.reqfactoront.com/content/datasets</t>
-        </is>
+          <t>http://reqfactoront.com/content/datasets</t>
+        </is>
+      </c>
+      <c r="C72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1303,6 +1521,9 @@
           <t>https://www.kaggle.com/datasets/computerscience3/public-requirementspure-dataset</t>
         </is>
       </c>
+      <c r="C73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1312,8 +1533,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/nltkdata/brown-corpus</t>
-        </is>
+          <t>https://www.kaggle.com/datasets/nltkdata/brown-corpus/data</t>
+        </is>
+      </c>
+      <c r="C74" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -1324,8 +1548,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.zenodo.org/doi/10.5281/zenodo.14513612</t>
-        </is>
+          <t>https://zenodo.org/doi/10.5281/zenodo.4530182</t>
+        </is>
+      </c>
+      <c r="C75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -1336,8 +1563,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.data.mendeley.com/datasets/7zbk8zsd8y/1</t>
-        </is>
+          <t>https://data.mendeley.com/datasets/7zbk8zsd8y/1</t>
+        </is>
+      </c>
+      <c r="C76" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -1351,6 +1581,9 @@
           <t>https://www.kaggle.com/datasets/mdahanafarifkhan/birdseye-ru</t>
         </is>
       </c>
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1360,8 +1593,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1145/3083187.3083214</t>
-        </is>
+          <t>https://doi.org/10.1145/3083187.3083214</t>
+        </is>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1372,8 +1608,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/FG.2019.8756593</t>
-        </is>
+          <t>https://doi.org/10.1109/FG.2019.8756593</t>
+        </is>
+      </c>
+      <c r="C79" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1384,8 +1623,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.arxiv.org/abs/2011.07689</t>
-        </is>
+          <t>https://arxiv.org/abs/2011.07689</t>
+        </is>
+      </c>
+      <c r="C80" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1396,8 +1638,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.universe.roboflow.com/face-detection-and-recognition-dataset/droneface</t>
-        </is>
+          <t>https://universe.roboflow.com/face-detection-and-recognition-dataset/droneface</t>
+        </is>
+      </c>
+      <c r="C81" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -1408,20 +1653,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.54822/QVHM1662</t>
-        </is>
+          <t>https://doi.org/10.54822/QVHM1662</t>
+        </is>
+      </c>
+      <c r="C82" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Otterloo-Burda-Utrecht_Housing_dataset_CSR2025.pdf</t>
+          <t>s41597-026-07353-6_reference.pdf</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by/4.0</t>
-        </is>
+          <t>http://creativecommons.org/licenses/by/4.0</t>
+        </is>
+      </c>
+      <c r="C83" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1435,6 +1686,9 @@
           <t>https://www.kaggle.com/datasets/ictinstitute/utrecht-housing-dataset</t>
         </is>
       </c>
+      <c r="C84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1447,6 +1701,9 @@
           <t>https://www.kaggle.com/datasets/shashanknecrothapa/ames-housing-dataset</t>
         </is>
       </c>
+      <c r="C85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1459,6 +1716,9 @@
           <t>https://www.kadaster.nl/winkel</t>
         </is>
       </c>
+      <c r="C86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1471,6 +1731,9 @@
           <t>https://www.funda.nl/</t>
         </is>
       </c>
+      <c r="C87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1483,6 +1746,9 @@
           <t>https://www.gps-coordinaten.nl/</t>
         </is>
       </c>
+      <c r="C88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1492,8 +1758,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.en.wikipedia.org/wiki/ISO_8601</t>
-        </is>
+          <t>https://en.wikipedia.org/wiki/ISO_8601</t>
+        </is>
+      </c>
+      <c r="C89" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1504,8 +1773,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1201/9780367816377</t>
-        </is>
+          <t>https://doi.org/10.1201/9780367816377</t>
+        </is>
+      </c>
+      <c r="C90" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -1516,8 +1788,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.fairmlbook.org</t>
-        </is>
+          <t>http://www.fairmlbook.org</t>
+        </is>
+      </c>
+      <c r="C91" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1528,8 +1803,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.data.europa.eu/eli/reg/2016/679/oj</t>
-        </is>
+          <t>http://data.europa.eu/eli/reg/2016/679/oj</t>
+        </is>
+      </c>
+      <c r="C92" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1540,8 +1818,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.fairlearn.org/main/user_guide/datasets/boston_housing_data.html</t>
-        </is>
+          <t>https://fairlearn.org/main/user_guide/datasets/boston_housing_data.html</t>
+        </is>
+      </c>
+      <c r="C93" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1552,8 +1833,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.peopleanalytics-regression-book.org/</t>
-        </is>
+          <t>https://peopleanalytics-regression-book.org/</t>
+        </is>
+      </c>
+      <c r="C94" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1564,8 +1848,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.academic.oup.com/jrssig/article/18/6/26/7038520</t>
-        </is>
+          <t>https://academic.oup.com/jrssig/article/18/6/26/7038520</t>
+        </is>
+      </c>
+      <c r="C95" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1576,20 +1863,26 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.jakevdp.github.io/PythonDataScienceHandbook</t>
-        </is>
+          <t>https://jakevdp.github.io/PythonDataScienceHandbook</t>
+        </is>
+      </c>
+      <c r="C96" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>essd-15-2117-2023.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2117-2023</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-15-3819-2023</t>
+        </is>
+      </c>
+      <c r="C97" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1600,8 +1893,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.earthquake.usgs.gov/earthquakes</t>
-        </is>
+          <t>https://earthquake.usgs.gov/earthquakes</t>
+        </is>
+      </c>
+      <c r="C98" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -1612,8 +1908,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.orfeus-eu.org/data/eida</t>
-        </is>
+          <t>http://www.orfeus-eu.org/data/eida</t>
+        </is>
+      </c>
+      <c r="C99" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -1624,8 +1923,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/ALPARRAY/Z3_2015</t>
-        </is>
+          <t>https://doi.org/10.12686/ALPARRAY/Z3_2015</t>
+        </is>
+      </c>
+      <c r="C100" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -1636,8 +1938,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/alparray/xt_2014</t>
-        </is>
+          <t>https://doi.org/10.12686/alparray/xt_2014</t>
+        </is>
+      </c>
+      <c r="C101" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -1648,8 +1953,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/BW</t>
-        </is>
+          <t>https://doi.org/10.7914/SN/BW</t>
+        </is>
+      </c>
+      <c r="C102" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -1660,8 +1968,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.12686/SED/NETWORKS/CH</t>
-        </is>
+          <t>https://doi.org/10.12686/SED/NETWORKS/CH</t>
+        </is>
+      </c>
+      <c r="C103" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -1672,8 +1983,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.25928/mbx6-hr74</t>
-        </is>
+          <t>https://doi.org/10.25928/mbx6-hr74</t>
+        </is>
+      </c>
+      <c r="C104" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -1684,8 +1998,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.13127/SD/X0FXNH7QFY</t>
-        </is>
+          <t>https://doi.org/10.13127/SD/X0FXNH7QFY</t>
+        </is>
+      </c>
+      <c r="C105" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -1696,8 +2013,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.13127/SD/fBBBtDtd6q</t>
-        </is>
+          <t>https://doi.org/10.13127/SD/fBBBtDtd6q</t>
+        </is>
+      </c>
+      <c r="C106" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -1708,8 +2028,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/NI</t>
-        </is>
+          <t>https://doi.org/10.7914/SN/NI</t>
+        </is>
+      </c>
+      <c r="C107" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -1720,8 +2043,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/OE</t>
-        </is>
+          <t>https://doi.org/10.7914/SN/OX</t>
+        </is>
+      </c>
+      <c r="C108" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -1732,8 +2058,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.15778/RESIF.FR</t>
-        </is>
+          <t>https://doi.org/10.15778/RESIF.FR</t>
+        </is>
+      </c>
+      <c r="C109" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -1747,6 +2076,9 @@
           <t>https://www.fdsn.org/networks/detail/SI</t>
         </is>
       </c>
+      <c r="C110" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1756,8 +2088,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/SL</t>
-        </is>
+          <t>https://doi.org/10.7914/SN/ST</t>
+        </is>
+      </c>
+      <c r="C111" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -1768,8 +2103,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.15778/RESIF.YP2012</t>
-        </is>
+          <t>https://doi.org/10.15778/RESIF.YP2012</t>
+        </is>
+      </c>
+      <c r="C112" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -1780,8 +2118,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7914/SN/ZJ_2019</t>
-        </is>
+          <t>https://doi.org/10.7914/SN/ZJ_2019</t>
+        </is>
+      </c>
+      <c r="C113" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -1792,8 +2133,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7695125</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.7695125</t>
+        </is>
+      </c>
+      <c r="C114" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -1804,8 +2148,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7937575</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.7937575</t>
+        </is>
+      </c>
+      <c r="C115" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -1816,8 +2163,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.rfmpy.readthedocs.io/en/latest/tutorial.html</t>
-        </is>
+          <t>https://rfmpy.readthedocs.io/en/latest/tutorial.html</t>
+        </is>
+      </c>
+      <c r="C116" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1828,8 +2178,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.github.com/kemichai/rfmpy</t>
-        </is>
+          <t>https://github.com/kemichai/rfmpy</t>
+        </is>
+      </c>
+      <c r="C117" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -1840,8 +2193,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.tecto.2013.08.004</t>
-        </is>
+          <t>https://doi.org/10.1016/j.tecto.2015.02.004</t>
+        </is>
+      </c>
+      <c r="C118" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -1852,8 +2208,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1785/gssrl.81.3.530</t>
-        </is>
+          <t>https://doi.org/10.1785/gssrl.81.3.530</t>
+        </is>
+      </c>
+      <c r="C119" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -1864,8 +2223,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.jog.2014.07.005</t>
-        </is>
+          <t>https://doi.org/10.1016/j.jog.2014.07.005</t>
+        </is>
+      </c>
+      <c r="C120" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -1876,8 +2238,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/se-12-1185-2021</t>
-        </is>
+          <t>https://doi.org/10.5194/se-12-1185-2021</t>
+        </is>
+      </c>
+      <c r="C121" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -1888,8 +2253,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1785/BSSA0820031453</t>
-        </is>
+          <t>https://doi.org/10.1785/BSSA0820031453</t>
+        </is>
+      </c>
+      <c r="C122" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1900,8 +2268,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1785/0220170151</t>
-        </is>
+          <t>https://doi.org/10.1785/0220170151</t>
+        </is>
+      </c>
+      <c r="C123" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -1912,8 +2283,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s40328-022-00394-4</t>
-        </is>
+          <t>https://doi.org/10.1007/s40328-022-00394-4</t>
+        </is>
+      </c>
+      <c r="C124" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -1924,8 +2298,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.5501399</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.5501399</t>
+        </is>
+      </c>
+      <c r="C125" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -1936,8 +2313,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2008.03985.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.2008.03919.x</t>
+        </is>
+      </c>
+      <c r="C126" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -1948,8 +2328,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2011GC003649</t>
-        </is>
+          <t>https://doi.org/10.1029/2011GC003649</t>
+        </is>
+      </c>
+      <c r="C127" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -1960,8 +2343,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1994.tb03942.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.1994.tb03942.x</t>
+        </is>
+      </c>
+      <c r="C128" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -1972,8 +2358,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1995.tb01837.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.1995.tb01837.x</t>
+        </is>
+      </c>
+      <c r="C129" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -1984,8 +2373,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.earscirev.2010.06.002</t>
-        </is>
+          <t>https://doi.org/10.1016/j.earscirev.2010.06.002</t>
+        </is>
+      </c>
+      <c r="C130" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -1996,8 +2388,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1785/0120050098</t>
-        </is>
+          <t>https://doi.org/10.1785/0120050098</t>
+        </is>
+      </c>
+      <c r="C131" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2008,8 +2403,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10712-018-9472-4</t>
-        </is>
+          <t>https://doi.org/10.1007/s10712-018-9472-4</t>
+        </is>
+      </c>
+      <c r="C132" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -2020,8 +2418,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.tecto.2018.07.001</t>
-        </is>
+          <t>https://doi.org/10.1016/j.tecto.2018.07.001</t>
+        </is>
+      </c>
+      <c r="C133" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -2032,8 +2433,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/MCSE.2007.55</t>
-        </is>
+          <t>https://doi.org/10.1109/MCSE.2007.55</t>
+        </is>
+      </c>
+      <c r="C134" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2044,8 +2448,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2021jb023160</t>
-        </is>
+          <t>https://doi.org/10.1029/2021jb023160</t>
+        </is>
+      </c>
+      <c r="C135" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -2056,8 +2463,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10950-019-09847-w</t>
-        </is>
+          <t>https://doi.org/10.1007/s10950-019-09847-w</t>
+        </is>
+      </c>
+      <c r="C136" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -2068,8 +2478,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2020JB021309</t>
-        </is>
+          <t>https://doi.org/10.1029/2020JB021309</t>
+        </is>
+      </c>
+      <c r="C137" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -2080,8 +2493,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1991.tb06724.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.1991.tb06724.x</t>
+        </is>
+      </c>
+      <c r="C138" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -2092,8 +2508,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/se-12-2503-2021</t>
-        </is>
+          <t>https://doi.org/10.5194/se-12-2503-2021</t>
+        </is>
+      </c>
+      <c r="C139" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -2104,8 +2523,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1126/science.283.5406.1306</t>
-        </is>
+          <t>https://doi.org/10.1126/science.283.5406.1306</t>
+        </is>
+      </c>
+      <c r="C140" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -2116,8 +2538,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1088/1749-4699/8/1/014003</t>
-        </is>
+          <t>https://doi.org/10.1088/1749-4699/8/1/014003</t>
+        </is>
+      </c>
+      <c r="C141" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -2128,8 +2553,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.epsl.2004.05.040</t>
-        </is>
+          <t>https://doi.org/10.1016/j.epsl.2004.05.040</t>
+        </is>
+      </c>
+      <c r="C142" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -2140,8 +2568,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1785/BSSA0670030713</t>
-        </is>
+          <t>https://doi.org/10.1785/BSSA0670030713</t>
+        </is>
+      </c>
+      <c r="C143" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -2152,8 +2583,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.1997.tb01220.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.1997.tb01220.x</t>
+        </is>
+      </c>
+      <c r="C144" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -2164,8 +2598,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1785/BSSA0890051395</t>
-        </is>
+          <t>https://doi.org/10.1785/BSSA0890051395</t>
+        </is>
+      </c>
+      <c r="C145" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -2176,8 +2613,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2007.03706.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.2007.03373.x</t>
+        </is>
+      </c>
+      <c r="C146" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -2188,8 +2628,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1093/gji/ggaa145</t>
-        </is>
+          <t>https://doi.org/10.1093/gji/ggaa145</t>
+        </is>
+      </c>
+      <c r="C147" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,8 +2643,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2018GC007743</t>
-        </is>
+          <t>https://doi.org/10.1029/2018GC007743</t>
+        </is>
+      </c>
+      <c r="C148" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -2212,8 +2658,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3389/feart.2021.742700</t>
-        </is>
+          <t>https://doi.org/10.3389/feart.2021.742700</t>
+        </is>
+      </c>
+      <c r="C149" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -2224,8 +2673,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-246X.2011.04940.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.2011.04940.x</t>
+        </is>
+      </c>
+      <c r="C150" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -2236,8 +2688,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.ringps.2020.100006</t>
-        </is>
+          <t>https://doi.org/10.1016/j.ringps.2020.100006</t>
+        </is>
+      </c>
+      <c r="C151" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -2248,8 +2703,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2022jb025141</t>
-        </is>
+          <t>https://doi.org/10.1029/2022jb025141</t>
+        </is>
+      </c>
+      <c r="C152" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -2260,8 +2718,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/97jb02122</t>
-        </is>
+          <t>https://doi.org/10.1029/97jb02122</t>
+        </is>
+      </c>
+      <c r="C153" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -2272,8 +2733,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1093/gji/ggab065</t>
-        </is>
+          <t>https://doi.org/10.1093/gji/ggab065</t>
+        </is>
+      </c>
+      <c r="C154" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -2284,8 +2748,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.epsl.2023.118096</t>
-        </is>
+          <t>https://doi.org/10.1016/j.epsl.2023.118096</t>
+        </is>
+      </c>
+      <c r="C155" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -2296,8 +2763,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1093/gji/ggab520</t>
-        </is>
+          <t>https://doi.org/10.1093/gji/ggab520</t>
+        </is>
+      </c>
+      <c r="C156" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -2308,8 +2778,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/se-12-2671-2021</t>
-        </is>
+          <t>https://doi.org/10.5194/se-12-2671-2021</t>
+        </is>
+      </c>
+      <c r="C157" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -2320,8 +2793,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1785/0119990122</t>
-        </is>
+          <t>https://doi.org/10.1785/0119990122</t>
+        </is>
+      </c>
+      <c r="C158" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -2332,8 +2808,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1046/j.1365-246X.2000.00077.x</t>
-        </is>
+          <t>https://doi.org/10.1046/j.1365-246X.2000.00077.x</t>
+        </is>
+      </c>
+      <c r="C159" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -2344,8 +2823,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3389/feart.2021.641113</t>
-        </is>
+          <t>https://doi.org/10.3389/feart.2021.641113</t>
+        </is>
+      </c>
+      <c r="C160" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -2356,8 +2838,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3389/feart.2021.671412</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-246X.2006.03086.x</t>
+        </is>
+      </c>
+      <c r="C161" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -2368,8 +2853,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s00015-004-1113-x</t>
-        </is>
+          <t>https://doi.org/10.3389/feart.2021.671412</t>
+        </is>
+      </c>
+      <c r="C162" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -2380,8 +2868,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1093/gji/ggt148</t>
-        </is>
+          <t>https://doi.org/10.1007/s00015-004-1113-x</t>
+        </is>
+      </c>
+      <c r="C163" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -2392,8 +2883,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/0031-9201(77)90008-5</t>
-        </is>
+          <t>https://doi.org/10.1093/gji/ggt148</t>
+        </is>
+      </c>
+      <c r="C164" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -2404,8 +2898,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1046/j.1365-246X.1998.00647.x</t>
-        </is>
+          <t>https://doi.org/10.1016/0031-9201(77)90008-5</t>
+        </is>
+      </c>
+      <c r="C165" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -2416,8 +2913,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2019GC008515</t>
-        </is>
+          <t>https://doi.org/10.1046/j.1365-246X.1998.00647.x</t>
+        </is>
+      </c>
+      <c r="C166" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -2428,8 +2928,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/97JB02379</t>
-        </is>
+          <t>https://doi.org/10.1029/2019GC008515</t>
+        </is>
+      </c>
+      <c r="C167" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -2440,8 +2943,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1130/G36833.1</t>
-        </is>
+          <t>https://doi.org/10.1029/97JB02379</t>
+        </is>
+      </c>
+      <c r="C168" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -2452,20 +2958,26 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/S0012-821X(00)00101-1</t>
-        </is>
+          <t>https://doi.org/10.1130/G36833.1</t>
+        </is>
+      </c>
+      <c r="C169" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>essd-16-525-2024.pdf</t>
+          <t>essd-15-2117-2023.pdf</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-525-2024</t>
-        </is>
+          <t>https://doi.org/10.1016/S0012-821X(00)00101-1</t>
+        </is>
+      </c>
+      <c r="C170" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -2476,8 +2988,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.hx3ffbgkh</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-16-525-2024</t>
+        </is>
+      </c>
+      <c r="C171" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -2488,8 +3003,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.fao.org/faostat/en</t>
-        </is>
+          <t>https://doi.org/10.5061/dryad.hx3ffbgkh</t>
+        </is>
+      </c>
+      <c r="C172" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -2500,8 +3018,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.fao.org/statistics/data-collection/en</t>
-        </is>
+          <t>https://www.fao.org/faostat/en</t>
+        </is>
+      </c>
+      <c r="C173" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -2512,8 +3033,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.cropnutrientdata.net</t>
-        </is>
+          <t>https://www.fao.org/statistics/data-collection/en</t>
+        </is>
+      </c>
+      <c r="C174" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -2524,8 +3048,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.10491879</t>
-        </is>
+          <t>http://www.cropnutrientdata.net</t>
+        </is>
+      </c>
+      <c r="C175" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -2536,8 +3063,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.10511851</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.10491880</t>
+        </is>
+      </c>
+      <c r="C176" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -2548,8 +3078,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/bg-9-4169-2012</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.10511851</t>
+        </is>
+      </c>
+      <c r="C177" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -2560,8 +3093,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/srep40366</t>
-        </is>
+          <t>https://doi.org/10.5194/bg-9-4169-2012</t>
+        </is>
+      </c>
+      <c r="C178" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -2572,8 +3108,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.documents1.worldbank.org/curated/en/827371554284501204/pdf/The-Greening-of-Farm-Support-Programs-International-Experiences-with-Agricultural-Subsidy-Reform.pdf</t>
-        </is>
+          <t>https://doi.org/10.1038/srep40366</t>
+        </is>
+      </c>
+      <c r="C179" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -2584,8 +3123,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.agee.2009.11.006</t>
-        </is>
+          <t>https://documents1.worldbank.org/curated/en/827371554284501204/pdf/The-Greening-of-Farm-Support-Programs-International-Experiences-with-Agricultural-Subsidy-Reform.pdf</t>
+        </is>
+      </c>
+      <c r="C180" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -2596,8 +3138,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/gbc.20053</t>
-        </is>
+          <t>https://doi.org/10.1016/j.agee.2009.11.006</t>
+        </is>
+      </c>
+      <c r="C181" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -2608,8 +3153,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.7133340</t>
-        </is>
+          <t>https://doi.org/10.1002/gbc.20053</t>
+        </is>
+      </c>
+      <c r="C182" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -2620,8 +3168,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10705-020-10064-y</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.7133336</t>
+        </is>
+      </c>
+      <c r="C183" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -2632,8 +3183,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-021-01061-z</t>
-        </is>
+          <t>https://doi.org/10.1007/s10705-020-10064-y</t>
+        </is>
+      </c>
+      <c r="C184" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -2644,8 +3198,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.fao.org/3/cc2904en/cc2904en.pdf</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-021-01061-z</t>
+        </is>
+      </c>
+      <c r="C185" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -2656,8 +3213,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.fenixservices.fao.org/faostat/static/documents/GU/GU_e.pdf</t>
-        </is>
+          <t>https://www.fao.org/3/cc2904en/cc2904en.pdf</t>
+        </is>
+      </c>
+      <c r="C186" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -2668,8 +3228,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.fao.org/3/cc0963en/cc0963en.pdf</t>
-        </is>
+          <t>https://fenixservices.fao.org/faostat/static/documents/GU/GU_e.pdf</t>
+        </is>
+      </c>
+      <c r="C187" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -2680,8 +3243,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11104-021-05166-7</t>
-        </is>
+          <t>https://www.fao.org/3/cc0963en/cc0963en.pdf</t>
+        </is>
+      </c>
+      <c r="C188" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -2692,8 +3258,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/gmd-13-5425-2020</t>
-        </is>
+          <t>https://doi.org/10.1007/s11104-021-05167-6</t>
+        </is>
+      </c>
+      <c r="C189" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -2704,8 +3273,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.ifastat.org/consumption/fertilizer-use-by-crop</t>
-        </is>
+          <t>https://doi.org/10.5194/gmd-13-5425-2020</t>
+        </is>
+      </c>
+      <c r="C190" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -2716,8 +3288,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.ifastat.org/databases/plant-nutrition</t>
-        </is>
+          <t>https://www.ifastat.org/consumption/fertilizer-use-by-crop</t>
+        </is>
+      </c>
+      <c r="C191" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -2728,8 +3303,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/pdf/1_Volume1/V1_3_Ch3_Uncertainties.pdf</t>
-        </is>
+          <t>https://www.ifastat.org/databases/plant-nutrition</t>
+        </is>
+      </c>
+      <c r="C192" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -2740,8 +3318,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.ec.europa.eu/eurostat/documents/2393397/2518760/Nutrient_Budgets_Handbook_(CPSA_AE_109)_corrected3.pdf/4a3647de-da73-4d23-b94b-e2b23844dc31</t>
-        </is>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/pdf/1_Volume1/V1_3_Ch3_Uncertainties.pdf</t>
+        </is>
+      </c>
+      <c r="C193" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -2752,8 +3333,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1088/1748-9326/9/10/105011</t>
-        </is>
+          <t>https://ec.europa.eu/eurostat/documents/2393397/2518760/Nutrient_Budgets_Handbook_(CPSA_AE_109)_corrected3.pdf/4a3647de-da73-4d23-b94b-e2b23844dc31</t>
+        </is>
+      </c>
+      <c r="C194" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -2764,8 +3348,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1088/1748-9326/11/9/095007</t>
-        </is>
+          <t>https://doi.org/10.1088/1748-9326/9/10/105011</t>
+        </is>
+      </c>
+      <c r="C195" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -2776,8 +3363,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10705-006-9078-y</t>
-        </is>
+          <t>https://doi.org/10.1088/1748-9326/11/9/095007</t>
+        </is>
+      </c>
+      <c r="C196" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -2788,8 +3378,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-9-181-2017</t>
-        </is>
+          <t>https://doi.org/10.1007/s10705-006-9078-y</t>
+        </is>
+      </c>
+      <c r="C197" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -2800,8 +3393,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.10492448</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-9-149-2017</t>
+        </is>
+      </c>
+      <c r="C198" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -2812,8 +3408,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-022-01592-z</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.10492448</t>
+        </is>
+      </c>
+      <c r="C199" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -2824,8 +3423,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.fcr.2022.108578</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-022-01592-z</t>
+        </is>
+      </c>
+      <c r="C200" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -2836,8 +3438,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.n2z34tn0x</t>
-        </is>
+          <t>https://doi.org/10.1016/j.fcr.2022.108578</t>
+        </is>
+      </c>
+      <c r="C201" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -2848,8 +3453,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/nature11420</t>
-        </is>
+          <t>https://doi.org/10.5061/dryad.n2z34tn0x</t>
+        </is>
+      </c>
+      <c r="C202" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -2860,8 +3468,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/S1161-0301(03)00067-4</t>
-        </is>
+          <t>https://doi.org/10.1038/nature11420</t>
+        </is>
+      </c>
+      <c r="C203" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -2872,8 +3483,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10705-009-9292-5</t>
-        </is>
+          <t>https://doi.org/10.1016/S1161-0301(03)00067-4</t>
+        </is>
+      </c>
+      <c r="C204" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -2884,8 +3498,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s43016-021-00263-3</t>
-        </is>
+          <t>https://doi.org/10.1007/s10705-009-9292-5</t>
+        </is>
+      </c>
+      <c r="C205" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -2896,8 +3513,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.ec.europa.eu/eurostat/documents/2393397/8259002/Grassland_2014_Task+2.pdf/42873c7f-dfdf-49ca-b2ef-7c7b5bcabfc8</t>
-        </is>
+          <t>https://doi.org/10.1038/s43016-021-00263-3</t>
+        </is>
+      </c>
+      <c r="C206" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -2908,8 +3528,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.scitotenv.2023.164249</t>
-        </is>
+          <t>https://ec.europa.eu/eurostat/documents/2393397/8259002/Grassland_2014_Task+2.pdf/42873c7f-dfdf-49ca-b2ef-7c7b5bcabfc8</t>
+        </is>
+      </c>
+      <c r="C207" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -2920,8 +3543,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/gcb.14741</t>
-        </is>
+          <t>https://doi.org/10.1016/j.scitotenv.2023.164249</t>
+        </is>
+      </c>
+      <c r="C208" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -2932,8 +3558,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1023/A:1023944131188</t>
-        </is>
+          <t>https://doi.org/10.1111/gcb.14741</t>
+        </is>
+      </c>
+      <c r="C209" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -2944,8 +3573,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.fao.org/documents/card/en/c/cb4549en</t>
-        </is>
+          <t>https://doi.org/10.1023/A:1023944131188</t>
+        </is>
+      </c>
+      <c r="C210" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -2956,8 +3588,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s43016-022-00667-9</t>
-        </is>
+          <t>http://www.fao.org/documents/card/en/c/cb4549en</t>
+        </is>
+      </c>
+      <c r="C211" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -2968,20 +3603,26 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-023-02385-8</t>
-        </is>
+          <t>https://doi.org/10.1038/s43016-022-00667-9</t>
+        </is>
+      </c>
+      <c r="C212" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>essd-16-525-2024.pdf</t>
+          <t>s41597-026-07353-6_reference.pdf</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1126/science.1170261</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-023-02895-5</t>
+        </is>
+      </c>
+      <c r="C213" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -2992,8 +3633,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1093/nsr/nwz087</t>
-        </is>
+          <t>https://doi.org/10.1126/science.1170261</t>
+        </is>
+      </c>
+      <c r="C214" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -3004,8 +3648,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/gcb.13766</t>
-        </is>
+          <t>https://doi.org/10.1093/nsr/nwz087</t>
+        </is>
+      </c>
+      <c r="C215" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -3016,8 +3663,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1126/science.1246067</t>
-        </is>
+          <t>https://doi.org/10.1111/gcb.13766</t>
+        </is>
+      </c>
+      <c r="C216" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -3028,8 +3678,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-023-02154-7</t>
-        </is>
+          <t>https://doi.org/10.1126/science.1246067</t>
+        </is>
+      </c>
+      <c r="C217" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -3040,8 +3693,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.scitotenv.2016.10.223</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-023-02154-7</t>
+        </is>
+      </c>
+      <c r="C218" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -3052,8 +3708,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/nature15743</t>
-        </is>
+          <t>https://doi.org/10.1016/j.scitotenv.2016.10.223</t>
+        </is>
+      </c>
+      <c r="C219" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -3064,8 +3723,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2018gb006060</t>
-        </is>
+          <t>https://doi.org/10.1038/nature15743</t>
+        </is>
+      </c>
+      <c r="C220" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -3076,8 +3738,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s43016-021-00318-5</t>
-        </is>
+          <t>https://doi.org/10.1029/2018gb006060</t>
+        </is>
+      </c>
+      <c r="C221" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -3088,20 +3753,26 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41586-022-05220-z</t>
-        </is>
+          <t>https://doi.org/10.1038/s43016-021-00318-5</t>
+        </is>
+      </c>
+      <c r="C222" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>essd-18-2397-2026.pdf</t>
+          <t>essd-16-525-2024.pdf</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-2397-2026</t>
-        </is>
+          <t>https://doi.org/10.1038/s41586-022-05220-z</t>
+        </is>
+      </c>
+      <c r="C223" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -3112,8 +3783,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17669443</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-18-2397-2026</t>
+        </is>
+      </c>
+      <c r="C224" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -3124,8 +3798,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.17669443</t>
+        </is>
+      </c>
+      <c r="C225" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -3136,20 +3813,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.19327966</t>
-        </is>
+          <t>https://user.eumetsat.int/catalogue/EO:EUM:DAT:MSG:HRSEVIRI</t>
+        </is>
+      </c>
+      <c r="C226" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>essd-18-2397-2026.pdf</t>
+          <t>s41597-025-04605-9.pdf</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41612-018-0046-4</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.13327692</t>
+        </is>
+      </c>
+      <c r="C227" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -3160,8 +3843,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/aerospace10070578</t>
-        </is>
+          <t>https://doi.org/10.1038/s41612-018-0046-4</t>
+        </is>
+      </c>
+      <c r="C228" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -3172,8 +3858,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-18-1115-2025</t>
-        </is>
+          <t>https://doi.org/10.3390/aerospace10070578</t>
+        </is>
+      </c>
+      <c r="C229" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -3184,8 +3873,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
-        </is>
+          <t>https://doi.org/10.5194/amt-18-1115-2025</t>
+        </is>
+      </c>
+      <c r="C230" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -3196,8 +3888,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.dib.2025.111364</t>
-        </is>
+          <t>https://www.eumetrain.org/sites/default/files/2022-10/RGB_recipes.pdf</t>
+        </is>
+      </c>
+      <c r="C231" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -3208,8 +3903,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2009JD012650</t>
-        </is>
+          <t>https://doi.org/10.1016/j.dib.2025.111364</t>
+        </is>
+      </c>
+      <c r="C232" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -3220,8 +3918,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1037/h0071325</t>
-        </is>
+          <t>https://doi.org/10.1029/2009JD012650</t>
+        </is>
+      </c>
+      <c r="C233" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -3232,8 +3933,11 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.atmosenv.2020.117834</t>
-        </is>
+          <t>https://doi.org/10.1037/h0071325</t>
+        </is>
+      </c>
+      <c r="C234" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -3244,8 +3948,11 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-3-655-2010</t>
-        </is>
+          <t>https://doi.org/10.1016/j.atmosenv.2020.117834</t>
+        </is>
+      </c>
+      <c r="C235" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -3256,8 +3963,11 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-17-4015-2024</t>
-        </is>
+          <t>https://doi.org/10.5194/amt-3-655-2010</t>
+        </is>
+      </c>
+      <c r="C236" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -3268,8 +3978,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-17-5161-2024</t>
-        </is>
+          <t>https://doi.org/10.5194/amt-17-4015-2024</t>
+        </is>
+      </c>
+      <c r="C237" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -3280,8 +3993,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1088/1748-9326/ac26f0</t>
-        </is>
+          <t>https://doi.org/10.5194/amt-17-5161-2024</t>
+        </is>
+      </c>
+      <c r="C238" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -3292,8 +4008,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/TGRS.2023.3345226</t>
-        </is>
+          <t>https://doi.org/10.1088/1748-9326/ac26f0</t>
+        </is>
+      </c>
+      <c r="C239" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -3304,8 +4023,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/acp-21-4285-2021</t>
-        </is>
+          <t>https://doi.org/10.1109/TGRS.2023.3345226</t>
+        </is>
+      </c>
+      <c r="C240" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -3316,8 +4038,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/1520-0477(2002)083</t>
-        </is>
+          <t>https://doi.org/10.5194/acp-21-4285-2021</t>
+        </is>
+      </c>
+      <c r="C241" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -3328,8 +4053,11 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/amt-10-3547-2017</t>
-        </is>
+          <t>https://doi.org/10.1175/1520-0477(2002)083</t>
+        </is>
+      </c>
+      <c r="C242" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -3340,8 +4068,11 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/acp-24-6071-2024</t>
-        </is>
+          <t>https://doi.org/10.5194/amt-10-4317-2017</t>
+        </is>
+      </c>
+      <c r="C243" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -3352,8 +4083,11 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5066/F7DF6PQS</t>
-        </is>
+          <t>https://doi.org/10.5194/acp-24-6071-2024</t>
+        </is>
+      </c>
+      <c r="C244" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -3364,8 +4098,11 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://www.v7labs.com/darwin</t>
-        </is>
+          <t>https://doi.org/10.5066/F7DF6PQS</t>
+        </is>
+      </c>
+      <c r="C245" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -3376,8 +4113,11 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/acp-15-8739-2015</t>
-        </is>
+          <t>https://www.v7labs.com/darwin</t>
+        </is>
+      </c>
+      <c r="C246" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -3388,8 +4128,11 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2024GL108452</t>
-        </is>
+          <t>https://doi.org/10.5194/acp-15-8739-2015</t>
+        </is>
+      </c>
+      <c r="C247" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -3400,20 +4143,26 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/acp-23-1941-2023</t>
-        </is>
+          <t>https://doi.org/10.1029/2024GL108452</t>
+        </is>
+      </c>
+      <c r="C248" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>s41597-025-04605-9.pdf</t>
+          <t>essd-18-2397-2026.pdf</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04605-9</t>
-        </is>
+          <t>https://doi.org/10.5194/acp-23-1941-2023</t>
+        </is>
+      </c>
+      <c r="C249" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -3424,8 +4173,11 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.orcid.org/0000-0002-1223-0861</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-025-04605-9</t>
+        </is>
+      </c>
+      <c r="C250" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -3436,8 +4188,11 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.orcid.org/0000-0002-5518-499X</t>
-        </is>
+          <t>http://orcid.org/0000-0002-1223-0861</t>
+        </is>
+      </c>
+      <c r="C251" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -3448,8 +4203,11 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.orcid.org/0000-0002-1576-0673</t>
-        </is>
+          <t>http://orcid.org/0000-0002-5518-499X</t>
+        </is>
+      </c>
+      <c r="C252" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -3460,8 +4218,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13329639</t>
-        </is>
+          <t>http://orcid.org/0000-0002-1576-0673</t>
+        </is>
+      </c>
+      <c r="C253" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -3472,8 +4233,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13327891</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.13329625</t>
+        </is>
+      </c>
+      <c r="C254" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -3484,8 +4248,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.12206815</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.13327891</t>
+        </is>
+      </c>
+      <c r="C255" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -3496,8 +4263,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14245751</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.12206815</t>
+        </is>
+      </c>
+      <c r="C256" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -3508,8 +4278,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.hdfgroup.org/solutions/hdf5</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.13329670</t>
+        </is>
+      </c>
+      <c r="C257" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -3520,8 +4293,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.nexusformat.org</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.14245751</t>
+        </is>
+      </c>
+      <c r="C258" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -3532,8 +4308,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.dawnsci.org</t>
-        </is>
+          <t>https://www.hdfgroup.org/solutions/hdf5</t>
+        </is>
+      </c>
+      <c r="C259" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -3544,8 +4323,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.imagej.net/software/fiji</t>
-        </is>
+          <t>https://www.nexusformat.org</t>
+        </is>
+      </c>
+      <c r="C260" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -3556,8 +4338,11 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arXiv.2301.11798</t>
-        </is>
+          <t>https://dawnsci.org</t>
+        </is>
+      </c>
+      <c r="C261" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -3568,8 +4353,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.32604/iasc.2023.030144</t>
-        </is>
+          <t>https://imagej.net/software/fiji</t>
+        </is>
+      </c>
+      <c r="C262" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -3580,8 +4368,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11042-020-08980-w</t>
-        </is>
+          <t>https://doi.org/10.48550/arXiv.2301.11798</t>
+        </is>
+      </c>
+      <c r="C263" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -3592,8 +4383,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/cnm.3381</t>
-        </is>
+          <t>https://doi.org/10.32604/iasc.2023.030144</t>
+        </is>
+      </c>
+      <c r="C264" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -3604,8 +4398,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/nmeth.3296</t>
-        </is>
+          <t>https://doi.org/10.1007/s11042-020-08980-w</t>
+        </is>
+      </c>
+      <c r="C265" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -3616,8 +4413,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/en15145115</t>
-        </is>
+          <t>https://doi.org/10.1002/cnm.3381</t>
+        </is>
+      </c>
+      <c r="C266" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -3628,8 +4428,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41467-021-26480-9</t>
-        </is>
+          <t>https://doi.org/10.1038/nmeth.3296</t>
+        </is>
+      </c>
+      <c r="C267" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -3640,20 +4443,26 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/aenm.202202407</t>
-        </is>
+          <t>https://doi.org/10.3390/en15145115</t>
+        </is>
+      </c>
+      <c r="C268" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>s41597-025-04605-9.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1039/C2EE22647B</t>
-        </is>
+          <t>https://doi.org/10.1038/s41467-021-24180-y</t>
+        </is>
+      </c>
+      <c r="C269" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -3664,8 +4473,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1039/F19757101671</t>
-        </is>
+          <t>https://doi.org/10.1002/aenm.202202407</t>
+        </is>
+      </c>
+      <c r="C270" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -3676,8 +4488,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arXiv.1610.08015</t>
-        </is>
+          <t>https://doi.org/10.1039/C2EE22647B</t>
+        </is>
+      </c>
+      <c r="C271" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -3688,8 +4503,11 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1107/S1600577521009875</t>
-        </is>
+          <t>https://doi.org/10.1039/F19757101671</t>
+        </is>
+      </c>
+      <c r="C272" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -3700,8 +4518,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1107/S1600577515002283</t>
-        </is>
+          <t>https://doi.org/10.48550/arXiv.1610.08015</t>
+        </is>
+      </c>
+      <c r="C273" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -3712,8 +4533,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1107/S1600577514013939</t>
-        </is>
+          <t>https://doi.org/10.1107/S1600577521009875</t>
+        </is>
+      </c>
+      <c r="C274" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -3724,8 +4548,11 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1107/S0909049512032864</t>
-        </is>
+          <t>https://doi.org/10.1107/S1600577515002283</t>
+        </is>
+      </c>
+      <c r="C275" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -3736,8 +4563,11 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.13349402</t>
-        </is>
+          <t>https://doi.org/10.1107/S1600577514013939</t>
+        </is>
+      </c>
+      <c r="C276" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -3748,8 +4578,11 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/nano12121960</t>
-        </is>
+          <t>https://doi.org/10.1107/S0909049512032864</t>
+        </is>
+      </c>
+      <c r="C277" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -3760,8 +4593,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1364/OE.23.032859</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.13349402</t>
+        </is>
+      </c>
+      <c r="C278" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -3772,56 +4608,71 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1107/S1600577522006300</t>
-        </is>
+          <t>https://doi.org/10.3390/nano12121960</t>
+        </is>
+      </c>
+      <c r="C279" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>s41597-025-04605-9.pdf</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-06866-4</t>
-        </is>
+          <t>https://doi.org/10.1364/OE.23.032859</t>
+        </is>
+      </c>
+      <c r="C280" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>s41597-025-04605-9.pdf</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6084/m9.figshare.30017944</t>
-        </is>
+          <t>https://doi.org/10.1107/S1600577522006300</t>
+        </is>
+      </c>
+      <c r="C281" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>s41597-026-06867-3.pdf</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.earthexplorer.usgs.gov/</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-026-06867-3</t>
+        </is>
+      </c>
+      <c r="C282" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>s41597-026-06867-3.pdf</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5066/F78P5XZM</t>
-        </is>
+          <t>https://doi.org/10.6084/M9</t>
+        </is>
+      </c>
+      <c r="C283" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -3832,8 +4683,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5066/F74X5684</t>
-        </is>
+          <t>https://earthexplorer.usgs.gov/</t>
+        </is>
+      </c>
+      <c r="C284" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -3844,8 +4698,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5066/F7WD3Z10</t>
-        </is>
+          <t>https://doi.org/10.5066/F78P5XZM</t>
+        </is>
+      </c>
+      <c r="C285" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -3856,8 +4713,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://www.earthexplorer.usgs.gov/scene/metadata/full/5e7c41f3ffaaf662/D3C1201-100004A040</t>
-        </is>
+          <t>https://doi.org/10.5066/F74X5684</t>
+        </is>
+      </c>
+      <c r="C286" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -3868,8 +4728,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1080/01402398408437182</t>
-        </is>
+          <t>https://doi.org/10.5066/F7WD3Z10</t>
+        </is>
+      </c>
+      <c r="C287" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -3880,8 +4743,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1179/009346910X12707320296838</t>
-        </is>
+          <t>https://earthexplorer.usgs.gov/scene/metadata/full</t>
+        </is>
+      </c>
+      <c r="C288" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -3892,8 +4758,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1080/02684527.2023.2219013</t>
-        </is>
+          <t>https://doi.org/10.1080/01402398408437182</t>
+        </is>
+      </c>
+      <c r="C289" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -3904,8 +4773,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.rse.2019.02.015</t>
-        </is>
+          <t>https://doi.org/10.1179/009346910X12707320296838</t>
+        </is>
+      </c>
+      <c r="C290" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -3916,20 +4788,26 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/rs14112593</t>
-        </is>
+          <t>https://doi.org/10.1080/02684527.2023.2219013</t>
+        </is>
+      </c>
+      <c r="C291" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>essd-17-7359-2025.pdf</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.isprsjprs.2014.09.005</t>
-        </is>
+          <t>https://doi.org/10.1016/j.rse.2016.02.054</t>
+        </is>
+      </c>
+      <c r="C292" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -3940,8 +4818,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.still.2024.106273</t>
-        </is>
+          <t>https://doi.org/10.3390/rs14112593</t>
+        </is>
+      </c>
+      <c r="C293" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -3952,8 +4833,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/rs15112793</t>
-        </is>
+          <t>https://doi.org/10.1016/j.isprsjprs.2014.09.005</t>
+        </is>
+      </c>
+      <c r="C294" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -3964,8 +4848,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.15184/aqy.2022.22</t>
-        </is>
+          <t>https://doi.org/10.1016/j.still.2024.106273</t>
+        </is>
+      </c>
+      <c r="C295" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -3976,8 +4863,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/land10100997</t>
-        </is>
+          <t>https://doi.org/10.3390/rs15112793</t>
+        </is>
+      </c>
+      <c r="C296" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -3988,8 +4878,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1126/sciadv.aav7266</t>
-        </is>
+          <t>https://doi.org/10.15184/aqy.2022.22</t>
+        </is>
+      </c>
+      <c r="C297" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -4000,8 +4893,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1177/2053019623121848</t>
-        </is>
+          <t>https://doi.org/10.3390/land10100997</t>
+        </is>
+      </c>
+      <c r="C298" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -4012,8 +4908,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1117/1</t>
-        </is>
+          <t>https://doi.org/10.1126/sciadv.aav7266</t>
+        </is>
+      </c>
+      <c r="C299" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -4024,8 +4923,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11852-023-00932-4</t>
-        </is>
+          <t>https://doi.org/10.1177/2053019623121848</t>
+        </is>
+      </c>
+      <c r="C300" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -4036,8 +4938,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.jhydrol.2025.133555</t>
-        </is>
+          <t>https://doi.org/10.1117/1</t>
+        </is>
+      </c>
+      <c r="C301" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -4048,8 +4953,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1109/JSTARS.2025.3582789</t>
-        </is>
+          <t>https://doi.org/10.1007/s11852-023-00932-4</t>
+        </is>
+      </c>
+      <c r="C302" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -4060,8 +4968,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.14358/PERS.85.2.109</t>
-        </is>
+          <t>https://doi.org/10.1016/j.jhydrol.2025.133555</t>
+        </is>
+      </c>
+      <c r="C303" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -4072,8 +4983,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1080/02684527.2015.1005495</t>
-        </is>
+          <t>https://doi.org/10.1109/JSTARS.2025.3582789</t>
+        </is>
+      </c>
+      <c r="C304" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -4084,8 +4998,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/s25103147</t>
-        </is>
+          <t>https://doi.org/10.14358/PERS.85.2.109</t>
+        </is>
+      </c>
+      <c r="C305" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -4096,8 +5013,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41598-024-81566-w</t>
-        </is>
+          <t>https://doi.org/10.1080/02684527.2015.1005495</t>
+        </is>
+      </c>
+      <c r="C306" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -4108,8 +5028,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.rse.2021.112586</t>
-        </is>
+          <t>https://doi.org/10.3390/s25103147</t>
+        </is>
+      </c>
+      <c r="C307" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -4120,8 +5043,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1080/00045608.2011.596357</t>
-        </is>
+          <t>https://doi.org/10.1038/s41598-024-81566-w</t>
+        </is>
+      </c>
+      <c r="C308" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -4132,8 +5058,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3389/feart.2020.566802</t>
-        </is>
+          <t>https://doi.org/10.1016/j.rse.2021.112586</t>
+        </is>
+      </c>
+      <c r="C309" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -4144,8 +5073,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.rse.2012.12.003</t>
-        </is>
+          <t>https://doi.org/10.1080/00045608.2011.596357</t>
+        </is>
+      </c>
+      <c r="C310" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -4156,32 +5088,41 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-3819-2023</t>
-        </is>
+          <t>https://doi.org/10.3389/feart.2020.566802</t>
+        </is>
+      </c>
+      <c r="C311" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>s41597-026-06866-4_reference.pdf</t>
+          <t>essd-17-7359-2025.pdf</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-12-563-2020</t>
-        </is>
+          <t>https://doi.org/10.1016/j.rse.2013.12.008</t>
+        </is>
+      </c>
+      <c r="C312" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>s41597-026-06867-3.pdf</t>
+          <t>s41597-026-06866-4_reference.pdf</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://www.api.biorxiv.org/details/server/interval/cursor/format</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-12-563-2020</t>
+        </is>
+      </c>
+      <c r="C313" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -4192,8 +5133,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/about/FAQ</t>
-        </is>
+          <t>https://api.biorxiv.org/details/server/interval/cursor/format</t>
+        </is>
+      </c>
+      <c r="C314" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -4204,8 +5148,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.api.crossref.org/works/doi</t>
-        </is>
+          <t>https://www.biorxiv.org/about/FAQ</t>
+        </is>
+      </c>
+      <c r="C315" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -4216,8 +5163,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1101/170381</t>
-        </is>
+          <t>https://api.crossref.org/works/doi</t>
+        </is>
+      </c>
+      <c r="C316" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -4228,8 +5178,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s00429-020-02136-0</t>
-        </is>
+          <t>https://doi.org/10.1101/170381</t>
+        </is>
+      </c>
+      <c r="C317" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -4240,8 +5193,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17992421</t>
-        </is>
+          <t>https://doi.org/10.1007/s00429-020-02136-0</t>
+        </is>
+      </c>
+      <c r="C318" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -4252,8 +5208,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://www.github.com/badalovafidan/preprint_to_paper_dataset</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.17992421</t>
+        </is>
+      </c>
+      <c r="C319" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -4264,8 +5223,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1371/journal.pbio.3000959</t>
-        </is>
+          <t>https://github.com/badalovafidan/preprint_to_paper_dataset</t>
+        </is>
+      </c>
+      <c r="C320" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -4276,8 +5238,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1371/journal.pone.0274441</t>
-        </is>
+          <t>https://doi.org/10.1371/journal.pbio.3000959</t>
+        </is>
+      </c>
+      <c r="C321" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -4288,8 +5253,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/leap.1265</t>
-        </is>
+          <t>https://doi.org/10.1371/journal.pone.0274441</t>
+        </is>
+      </c>
+      <c r="C322" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -4300,8 +5268,11 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11192-021-03900-7</t>
-        </is>
+          <t>https://doi.org/10.1002/leap.1265</t>
+        </is>
+      </c>
+      <c r="C323" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -4312,8 +5283,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1101/833400</t>
-        </is>
+          <t>https://doi.org/10.1007/s11192-021-03900-7</t>
+        </is>
+      </c>
+      <c r="C324" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -4324,8 +5298,11 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7554/eLife.45133</t>
-        </is>
+          <t>https://doi.org/10.1101/833400</t>
+        </is>
+      </c>
+      <c r="C325" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -4336,8 +5313,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11192-021-04059-x</t>
-        </is>
+          <t>https://doi.org/10.7554/eLife.45133</t>
+        </is>
+      </c>
+      <c r="C326" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -4348,8 +5328,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11192-022-04346-1</t>
-        </is>
+          <t>https://doi.org/10.1007/s11192-021-04059-x</t>
+        </is>
+      </c>
+      <c r="C327" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -4360,8 +5343,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.4103/sja.sja_632_21</t>
-        </is>
+          <t>https://doi.org/10.1007/s11192-022-04346-1</t>
+        </is>
+      </c>
+      <c r="C328" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -4372,8 +5358,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.7554/eLife.58496</t>
-        </is>
+          <t>https://doi.org/10.4103/sja.sja_632_21</t>
+        </is>
+      </c>
+      <c r="C329" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -4384,8 +5373,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1162/qss_a_00043</t>
-        </is>
+          <t>https://doi.org/10.7554/eLife.58496</t>
+        </is>
+      </c>
+      <c r="C330" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -4396,8 +5388,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/ZENODO.2529922</t>
-        </is>
+          <t>https://doi.org/10.1162/qss_a_00043</t>
+        </is>
+      </c>
+      <c r="C331" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -4408,8 +5403,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1371/journal.pone.0303005</t>
-        </is>
+          <t>https://doi.org/10.5281/ZENODO.2529922</t>
+        </is>
+      </c>
+      <c r="C332" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -4420,8 +5418,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1371/journal.pone.0281659</t>
-        </is>
+          <t>https://doi.org/10.1371/journal.pone.0303005</t>
+        </is>
+      </c>
+      <c r="C333" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -4432,8 +5433,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15124417</t>
-        </is>
+          <t>https://doi.org/10.1371/journal.pone.0281659</t>
+        </is>
+      </c>
+      <c r="C334" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -4444,8 +5448,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1177/001316446002000104</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.15124417</t>
+        </is>
+      </c>
+      <c r="C335" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -4456,8 +5463,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.11613/BM.2012.031</t>
-        </is>
+          <t>https://doi.org/10.1177/001316446002000104</t>
+        </is>
+      </c>
+      <c r="C336" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -4468,8 +5478,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.6028/NBS.RPT.9011</t>
-        </is>
+          <t>https://doi.org/10.11613/BM.2012.031</t>
+        </is>
+      </c>
+      <c r="C337" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -4480,8 +5493,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41562-024-01833-8</t>
-        </is>
+          <t>https://doi.org/10.6028/NBS.RPT.9011</t>
+        </is>
+      </c>
+      <c r="C338" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -4492,8 +5508,11 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/nj7612-457a</t>
-        </is>
+          <t>https://doi.org/10.1038/s41562-024-01833-8</t>
+        </is>
+      </c>
+      <c r="C339" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -4504,8 +5523,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1126/science.368.6494.924</t>
-        </is>
+          <t>https://doi.org/10.1038/nj7612-457a</t>
+        </is>
+      </c>
+      <c r="C340" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -4516,8 +5538,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/asi.24852</t>
-        </is>
+          <t>https://doi.org/10.1126/science.368.6494.924</t>
+        </is>
+      </c>
+      <c r="C341" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -4528,8 +5553,11 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/d41586-017-08404-0</t>
-        </is>
+          <t>https://doi.org/10.1002/asi.24852</t>
+        </is>
+      </c>
+      <c r="C342" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -4540,8 +5568,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.joi.2013.08.006</t>
-        </is>
+          <t>https://doi.org/10.1038/d41586-017-08404-0</t>
+        </is>
+      </c>
+      <c r="C343" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -4552,8 +5583,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/asi.23209</t>
-        </is>
+          <t>https://doi.org/10.1016/j.joi.2013.08.006</t>
+        </is>
+      </c>
+      <c r="C344" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -4564,8 +5598,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1098/rsos.160140</t>
-        </is>
+          <t>https://doi.org/10.1002/asi.23209</t>
+        </is>
+      </c>
+      <c r="C345" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -4576,8 +5613,11 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.21105/joss.01686</t>
-        </is>
+          <t>https://doi.org/10.1098/rsos.160140</t>
+        </is>
+      </c>
+      <c r="C346" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -4588,8 +5628,11 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.32614/CRAN.package.cowplot</t>
-        </is>
+          <t>https://doi.org/10.21105/joss.01686</t>
+        </is>
+      </c>
+      <c r="C347" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -4600,8 +5643,11 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.32614/CRAN.package.psych</t>
-        </is>
+          <t>https://doi.org/10.32614/CRAN.package.cowplot</t>
+        </is>
+      </c>
+      <c r="C348" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -4612,8 +5658,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.18637/jss.v028.i05</t>
-        </is>
+          <t>https://doi.org/10.32614/CRAN.package.psych</t>
+        </is>
+      </c>
+      <c r="C349" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -4624,8 +5673,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.ominoproject.eu</t>
-        </is>
+          <t>https://doi.org/10.18637/jss.v028.i05</t>
+        </is>
+      </c>
+      <c r="C350" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -4636,20 +5688,26 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.nature.com/reprints</t>
-        </is>
+          <t>http://ominoproject.eu</t>
+        </is>
+      </c>
+      <c r="C351" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>s41597-026-07203-5_reference.pdf</t>
+          <t>s41597-026-06867-3.pdf</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-07203-5</t>
-        </is>
+          <t>http://www.nature.com/reprints</t>
+        </is>
+      </c>
+      <c r="C352" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -4660,8 +5718,11 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://www.creativecommons.org/licenses/by-nc-nd/4.0</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-026-07203-5</t>
+        </is>
+      </c>
+      <c r="C353" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -4672,8 +5733,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.15096167</t>
-        </is>
+          <t>http://creativecommons.org/licenses/by-nc-nd/4.0</t>
+        </is>
+      </c>
+      <c r="C354" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -4684,8 +5748,11 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.2166/ws.2018.129</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.15096167</t>
+        </is>
+      </c>
+      <c r="C355" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -4696,8 +5763,11 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.proeng.2014.02.157</t>
-        </is>
+          <t>https://doi.org/10.2166/ws.2018.129</t>
+        </is>
+      </c>
+      <c r="C356" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -4708,8 +5778,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1080/15730621003610878</t>
-        </is>
+          <t>https://doi.org/10.1016/j.proeng.2014.02.157</t>
+        </is>
+      </c>
+      <c r="C357" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -4720,8 +5793,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.arcontrol.2023.03.012</t>
-        </is>
+          <t>https://doi.org/10.1080/15730621003610878</t>
+        </is>
+      </c>
+      <c r="C358" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -4732,8 +5808,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.proeng.2015.08.851</t>
-        </is>
+          <t>https://doi.org/10.1016/j.arcontrol.2023.03.012</t>
+        </is>
+      </c>
+      <c r="C359" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -4744,8 +5823,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.2166/hydro.2021.093</t>
-        </is>
+          <t>https://doi.org/10.1016/j.proeng.2015.08.851</t>
+        </is>
+      </c>
+      <c r="C360" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -4756,8 +5838,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.procs.2024.06.347</t>
-        </is>
+          <t>https://doi.org/10.2166/hydro.2021.093</t>
+        </is>
+      </c>
+      <c r="C361" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -4768,8 +5853,11 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/dwes-13-29-2020</t>
-        </is>
+          <t>https://doi.org/10.1016/j.procs.2024.06.347</t>
+        </is>
+      </c>
+      <c r="C362" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -4780,8 +5868,11 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.eureau.org/</t>
-        </is>
+          <t>https://doi.org/10.5194/dwes-13-29-2020</t>
+        </is>
+      </c>
+      <c r="C363" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -4792,8 +5883,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://www.academia.edu/42079490</t>
-        </is>
+          <t>https://www.eureau.org/</t>
+        </is>
+      </c>
+      <c r="C364" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -4804,8 +5898,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/978-0-387-84858-7</t>
-        </is>
+          <t>https://www.academia.edu/42079490</t>
+        </is>
+      </c>
+      <c r="C365" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -4816,8 +5913,11 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.elastic.co/guide/en/machine-learning/current/ml-anomaly-detection-job-types.html</t>
-        </is>
+          <t>https://doi.org/10.1007/978-0-387-84858-7</t>
+        </is>
+      </c>
+      <c r="C366" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -4828,8 +5928,11 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.ibm.com/think/topics/machine-learning-for-anomaly-detection</t>
-        </is>
+          <t>https://www.elastic.co/guide/en/machine-learning/current/ml-anomaly-detection-job-types.html</t>
+        </is>
+      </c>
+      <c r="C367" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -4840,20 +5943,26 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.2307/2281536</t>
-        </is>
+          <t>https://www.ibm.com/think/topics/machine-learning-for-anomaly-detection</t>
+        </is>
+      </c>
+      <c r="C368" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>s41597-026-07353-6_reference.pdf</t>
+          <t>s41597-026-07203-5_reference.pdf</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-026-07353-6</t>
-        </is>
+          <t>https://doi.org/10.2307/2281536</t>
+        </is>
+      </c>
+      <c r="C369" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -4864,8 +5973,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.14260400</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-026-07353-6</t>
+        </is>
+      </c>
+      <c r="C370" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -4876,8 +5988,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41561-024-01483-5</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.14260400</t>
+        </is>
+      </c>
+      <c r="C371" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="372">
@@ -4888,8 +6003,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/hess-23-3603-2019</t>
-        </is>
+          <t>https://doi.org/10.1038/s41561-024-01483-5</t>
+        </is>
+      </c>
+      <c r="C372" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -4900,8 +6018,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.hydrol-earth-syst-sci.net/23/3603/2019/hess-23-3603-2019.html</t>
-        </is>
+          <t>https://doi.org/10.5194/hess-23-3603-2019</t>
+        </is>
+      </c>
+      <c r="C373" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -4912,8 +6033,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10040-013-0969-0</t>
-        </is>
+          <t>https://www.hydrol-earth-syst-sci.net/23/3603/2019/hess-23-3603-2019.html</t>
+        </is>
+      </c>
+      <c r="C374" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -4924,8 +6048,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/gwat.13195</t>
-        </is>
+          <t>https://doi.org/10.1007/s10040-013-0969-0</t>
+        </is>
+      </c>
+      <c r="C375" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -4936,8 +6063,11 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10040-023-02759-7</t>
-        </is>
+          <t>https://doi.org/10.1111/gwat.13195</t>
+        </is>
+      </c>
+      <c r="C376" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -4948,8 +6078,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2025JH000703</t>
-        </is>
+          <t>https://doi.org/10.1007/s10040-023-02759-7</t>
+        </is>
+      </c>
+      <c r="C377" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -4960,8 +6093,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.hess.copernicus.org/articles/21/5293/2017</t>
-        </is>
+          <t>https://doi.org/10.1029/2025JH000703</t>
+        </is>
+      </c>
+      <c r="C378" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -4972,8 +6108,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.essd.copernicus.org/articles/15/5755/2023</t>
-        </is>
+          <t>https://hess.copernicus.org/articles/21/5293/2017</t>
+        </is>
+      </c>
+      <c r="C379" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -4984,8 +6123,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.scitotenv.2020.137042</t>
-        </is>
+          <t>https://essd.copernicus.org/articles/15/5755/2023</t>
+        </is>
+      </c>
+      <c r="C380" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -4996,8 +6138,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-019-0346-5</t>
-        </is>
+          <t>https://doi.org/10.1016/j.scitotenv.2020.137042</t>
+        </is>
+      </c>
+      <c r="C381" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -5008,8 +6153,11 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.app.readcube.com/library/undefined/item/acdd2a94-1f0e-4d64-95cc-beb95236e5b7</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-019-0346-5</t>
+        </is>
+      </c>
+      <c r="C382" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -5020,8 +6168,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-04799-y</t>
-        </is>
+          <t>https://app.readcube.com/library/undefined/item/acdd2a94-1f0e-4d64-95cc-beb95236e5b7</t>
+        </is>
+      </c>
+      <c r="C383" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -5032,8 +6183,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-025-05843-7</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-025-04799-y</t>
+        </is>
+      </c>
+      <c r="C384" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -5044,8 +6198,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s43247-024-01554-w</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-025-05843-7</t>
+        </is>
+      </c>
+      <c r="C385" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -5056,8 +6213,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.essd.copernicus.org/preprints/essd-2025-321</t>
-        </is>
+          <t>https://doi.org/10.1038/s43247-024-01554-w</t>
+        </is>
+      </c>
+      <c r="C386" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -5068,8 +6228,11 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.ggmn.un-igrac.org</t>
-        </is>
+          <t>https://essd.copernicus.org/preprints/essd-2025-321</t>
+        </is>
+      </c>
+      <c r="C387" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -5080,8 +6243,11 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.58154/6Z0Y-DA34</t>
-        </is>
+          <t>https://ggmn.un-igrac.org</t>
+        </is>
+      </c>
+      <c r="C388" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -5092,8 +6258,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.31223/X5673T</t>
-        </is>
+          <t>https://doi.org/10.58154/6Z0Y-DA34</t>
+        </is>
+      </c>
+      <c r="C389" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -5104,8 +6273,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2006WR005653</t>
-        </is>
+          <t>https://doi.org/10.31223/X5673T</t>
+        </is>
+      </c>
+      <c r="C390" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -5116,8 +6288,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10040-006-0136-y</t>
-        </is>
+          <t>https://doi.org/10.1029/2006WR005653</t>
+        </is>
+      </c>
+      <c r="C391" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -5128,8 +6303,11 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.tc.copernicus.org/articles/19/4391/2025</t>
-        </is>
+          <t>https://doi.org/10.1007/s10040-006-0136-y</t>
+        </is>
+      </c>
+      <c r="C392" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -5140,8 +6318,11 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s12665-018-7228-6</t>
-        </is>
+          <t>https://tc.copernicus.org/articles/19/4391/2025</t>
+        </is>
+      </c>
+      <c r="C393" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -5152,8 +6333,11 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.onlinelibrary.wiley.com/doi/10.1029/2004WR003726/abstract</t>
-        </is>
+          <t>https://doi.org/10.1007/s12665-018-7228-6</t>
+        </is>
+      </c>
+      <c r="C394" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -5164,8 +6348,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/WR020i006p00727</t>
-        </is>
+          <t>http://onlinelibrary.wiley.com/doi/10.1029/2004WR003726/abstract</t>
+        </is>
+      </c>
+      <c r="C395" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -5176,8 +6363,11 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://www.hess.copernicus.org/articles/29/6221/2025</t>
-        </is>
+          <t>https://doi.org/10.1029/WR020i006p00727</t>
+        </is>
+      </c>
+      <c r="C396" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -5188,8 +6378,11 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/gwat.13474</t>
-        </is>
+          <t>https://hess.copernicus.org/articles/29/6221/2025</t>
+        </is>
+      </c>
+      <c r="C397" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -5200,8 +6393,11 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.gmd.copernicus.org/articles/17/7083/2024</t>
-        </is>
+          <t>https://doi.org/10.1111/gwat.13474</t>
+        </is>
+      </c>
+      <c r="C398" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -5212,8 +6408,11 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0022169423010624</t>
-        </is>
+          <t>https://gmd.copernicus.org/articles/17/7083/2024</t>
+        </is>
+      </c>
+      <c r="C399" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -5224,8 +6423,11 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://www.opendata.swiss/de/dataset/geologische-karte-der-schweiz-1-500000</t>
-        </is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0022169423010624</t>
+        </is>
+      </c>
+      <c r="C400" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -5236,8 +6438,11 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1371/journal.pone.0169748</t>
-        </is>
+          <t>https://opendata.swiss/de/dataset/geologische-karte-der-schweiz-1-500000</t>
+        </is>
+      </c>
+      <c r="C401" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="402">
@@ -5248,8 +6453,11 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.2909/ddacbd5e-068f-4e52-a596-d606e8de7f40</t>
-        </is>
+          <t>https://doi.org/10.1371/journal.pone.0169748</t>
+        </is>
+      </c>
+      <c r="C402" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -5260,8 +6468,11 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.opendata.swiss/de/dataset/hydrogeologische-karte-der-schweiz-grundwasservorkommen-1-500000</t>
-        </is>
+          <t>https://doi.org/10.2909/ddacbd5e-068f-4e52-a596-d606e8de7f40</t>
+        </is>
+      </c>
+      <c r="C403" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -5272,8 +6483,11 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.agupubs.onlinelibrary.wiley.com/doi/abs/10.1029/2018WR024418</t>
-        </is>
+          <t>https://opendata.swiss/de/dataset/hydrogeologische-karte-der-schweiz-grundwasservorkommen-1-500000</t>
+        </is>
+      </c>
+      <c r="C404" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -5284,8 +6498,11 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/gwat.13486</t>
-        </is>
+          <t>https://agupubs.onlinelibrary.wiley.com/doi/abs/10.1029/2018WR024418</t>
+        </is>
+      </c>
+      <c r="C405" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -5296,8 +6513,11 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.amtsdruckschriften.bar.admin.ch/detailView.do?id=10045204</t>
-        </is>
+          <t>https://doi.org/10.1111/gwat.13486</t>
+        </is>
+      </c>
+      <c r="C406" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -5308,8 +6528,11 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0022169422008496</t>
-        </is>
+          <t>https://www.amtsdruckschriften.bar.admin.ch/detailView.do?id=10045204</t>
+        </is>
+      </c>
+      <c r="C407" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -5320,20 +6543,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.boris-portal.unibe.ch/handle/20.500.12422/76902</t>
-        </is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0022169422008496</t>
+        </is>
+      </c>
+      <c r="C408" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>usenixsecurity24-appendix-lopez-morales.pdf</t>
+          <t>s41597-026-07353-6_reference.pdf</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.usenix.org/conference/usenixsecurity24/presentation/lopez-morales</t>
-        </is>
+          <t>https://boris-portal.unibe.ch/handle/20.500.12422/76902</t>
+        </is>
+      </c>
+      <c r="C409" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -5344,8 +6573,11 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/plc-sok-dataset</t>
-        </is>
+          <t>https://www.usenix.org/conference/usenixsecurity24/presentation/lopez-morales</t>
+        </is>
+      </c>
+      <c r="C410" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -5356,8 +6588,11 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.github.com/efrenlopezm/ics2matrix</t>
-        </is>
+          <t>https://github.com/efrenlopezm/plc-sok-dataset</t>
+        </is>
+      </c>
+      <c r="C411" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -5368,20 +6603,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.secartifacts.github.io/usenixsec2024</t>
-        </is>
+          <t>https://github.com/efrenlopezm/ics2matrix</t>
+        </is>
+      </c>
+      <c r="C412" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>essd-13-5337-2021.pdf</t>
+          <t>usenixsecurity24-appendix-lopez-morales.pdf</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-13-5337-2021</t>
-        </is>
+          <t>https://secartifacts.github.io/usenixsec2024</t>
+        </is>
+      </c>
+      <c r="C413" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -5392,8 +6633,11 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.6hdr7sqzx</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-13-5337-2021</t>
+        </is>
+      </c>
+      <c r="C414" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="415">
@@ -5404,8 +6648,11 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.usgs.gov/centers/eros/science</t>
-        </is>
+          <t>https://doi.org/10.5061/dryad.6hdr7sqzx</t>
+        </is>
+      </c>
+      <c r="C415" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -5416,8 +6663,11 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://www.lpdaac.usgs.gov/products/mod13a3v006</t>
-        </is>
+          <t>https://www.usgs.gov/centers/eros/science</t>
+        </is>
+      </c>
+      <c r="C416" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -5428,8 +6678,11 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/gcb.13691</t>
-        </is>
+          <t>https://lpdaac.usgs.gov/products/mod13a3v006</t>
+        </is>
+      </c>
+      <c r="C417" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -5440,8 +6693,11 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/BF00000889</t>
-        </is>
+          <t>https://doi.org/10.1111/gcb.13691</t>
+        </is>
+      </c>
+      <c r="C418" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -5452,8 +6708,11 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/S0378-1127(02)00234-7</t>
-        </is>
+          <t>https://doi.org/10.1007/BF00000889</t>
+        </is>
+      </c>
+      <c r="C419" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -5464,8 +6723,11 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/S0065-2113(08)60845-7</t>
-        </is>
+          <t>https://doi.org/10.1016/S0378-1127(02)00234-7</t>
+        </is>
+      </c>
+      <c r="C420" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -5476,8 +6738,11 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1093/treephys/tpx038</t>
-        </is>
+          <t>https://doi.org/10.1016/S0065-2113(08)60845-7</t>
+        </is>
+      </c>
+      <c r="C421" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="422">
@@ -5488,8 +6753,11 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/BF00195729</t>
-        </is>
+          <t>https://doi.org/10.1093/treephys/tpx038</t>
+        </is>
+      </c>
+      <c r="C422" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -5500,8 +6768,11 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1365-3040.2004.01181.x</t>
-        </is>
+          <t>https://doi.org/10.1007/BF00195729</t>
+        </is>
+      </c>
+      <c r="C423" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -5512,8 +6783,11 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41893-019-0220-7</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1365-3040.2004.01181.x</t>
+        </is>
+      </c>
+      <c r="C424" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="425">
@@ -5524,8 +6798,11 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1302768110</t>
-        </is>
+          <t>https://doi.org/10.1038/s41893-019-0220-7</t>
+        </is>
+      </c>
+      <c r="C425" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -5536,8 +6813,11 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1046/j.1365-2486.2001.00383.x</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.1302768110</t>
+        </is>
+      </c>
+      <c r="C426" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -5548,8 +6828,11 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/ngeo2516</t>
-        </is>
+          <t>https://doi.org/10.1046/j.1365-2486.2001.00383.x</t>
+        </is>
+      </c>
+      <c r="C427" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -5560,8 +6843,11 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41561-019-0530-4</t>
-        </is>
+          <t>https://doi.org/10.1038/ngeo721</t>
+        </is>
+      </c>
+      <c r="C428" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -5572,8 +6858,11 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1046/j.1461-0248.2003.00518.x</t>
-        </is>
+          <t>https://doi.org/10.1038/s41561-019-0530-4</t>
+        </is>
+      </c>
+      <c r="C429" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -5584,8 +6873,11 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1461-0248.2007.01113.x</t>
-        </is>
+          <t>https://doi.org/10.1046/j.1461-0248.2003.00518.x</t>
+        </is>
+      </c>
+      <c r="C430" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -5596,8 +6888,11 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1469-8137.2010.03214.x</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1461-0248.2007.01113.x</t>
+        </is>
+      </c>
+      <c r="C431" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -5608,8 +6903,11 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/ece3.3630</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1469-8137.2010.03214.x</t>
+        </is>
+      </c>
+      <c r="C432" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -5620,8 +6918,11 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/nph.15451</t>
-        </is>
+          <t>https://doi.org/10.1002/ece3.3630</t>
+        </is>
+      </c>
+      <c r="C433" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -5632,8 +6933,11 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41477-019-0549-y</t>
-        </is>
+          <t>https://doi.org/10.1111/nph.15451</t>
+        </is>
+      </c>
+      <c r="C434" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -5644,8 +6948,11 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/BF00379710</t>
-        </is>
+          <t>https://doi.org/10.1038/s41477-019-0549-y</t>
+        </is>
+      </c>
+      <c r="C435" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -5656,8 +6963,11 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.0706518104</t>
-        </is>
+          <t>https://doi.org/10.1007/BF00379710</t>
+        </is>
+      </c>
+      <c r="C436" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -5668,8 +6978,11 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2011GB004252</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.0706518104</t>
+        </is>
+      </c>
+      <c r="C437" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -5680,8 +6993,11 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41561-019-0404-9</t>
-        </is>
+          <t>https://doi.org/10.1029/2011GB004252</t>
+        </is>
+      </c>
+      <c r="C438" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -5692,8 +7008,11 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/0012-8252(95)00049-6</t>
-        </is>
+          <t>https://doi.org/10.1038/s41561-019-0404-9</t>
+        </is>
+      </c>
+      <c r="C439" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -5704,8 +7023,11 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41467-020-14492-w</t>
-        </is>
+          <t>https://doi.org/10.1016/0012-8252(95)00049-6</t>
+        </is>
+      </c>
+      <c r="C440" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -5716,8 +7038,11 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1126/science.1091390</t>
-        </is>
+          <t>https://doi.org/10.1038/s41467-020-14492-w</t>
+        </is>
+      </c>
+      <c r="C441" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="442">
@@ -5728,8 +7053,11 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/nplants.2016.24</t>
-        </is>
+          <t>https://doi.org/10.1126/science.1091390</t>
+        </is>
+      </c>
+      <c r="C442" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="443">
@@ -5740,8 +7068,11 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1201/9781420025293</t>
-        </is>
+          <t>https://doi.org/10.1038/nplants.2016.24</t>
+        </is>
+      </c>
+      <c r="C443" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -5752,8 +7083,11 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1139/x87-165</t>
-        </is>
+          <t>https://doi.org/10.1201/9781420025293</t>
+        </is>
+      </c>
+      <c r="C444" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -5764,8 +7098,11 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.0701424104</t>
-        </is>
+          <t>https://doi.org/10.1139/x87-165</t>
+        </is>
+      </c>
+      <c r="C445" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -5776,8 +7113,11 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s11104-017-3234-9</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.0701424104</t>
+        </is>
+      </c>
+      <c r="C446" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -5788,8 +7128,11 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1890/06-2057.1</t>
-        </is>
+          <t>https://doi.org/10.1007/s11104-017-3234-9</t>
+        </is>
+      </c>
+      <c r="C447" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -5800,8 +7143,11 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-10-405-2018</t>
-        </is>
+          <t>https://doi.org/10.1890/06-2057.1</t>
+        </is>
+      </c>
+      <c r="C448" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="449">
@@ -5812,8 +7158,11 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1046/j.0269-8463.2004.00805.x</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-10-405-2018</t>
+        </is>
+      </c>
+      <c r="C449" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="450">
@@ -5824,8 +7173,11 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/j.1469-8137.2006.01851.x</t>
-        </is>
+          <t>https://doi.org/10.1046/j.0269-8463.2004.00805.x</t>
+        </is>
+      </c>
+      <c r="C450" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -5836,8 +7188,11 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1700294115</t>
-        </is>
+          <t>https://doi.org/10.1111/j.1469-8137.2006.01851.x</t>
+        </is>
+      </c>
+      <c r="C451" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -5848,8 +7203,11 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1641/0006-3568(2004)054</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.1700295114</t>
+        </is>
+      </c>
+      <c r="C452" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -5860,8 +7218,11 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/S0378-1127(99)00207-8</t>
-        </is>
+          <t>https://doi.org/10.1641/0006-3568(2004)054</t>
+        </is>
+      </c>
+      <c r="C453" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -5872,8 +7233,11 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.jhydrol.2007.02.018</t>
-        </is>
+          <t>https://doi.org/10.1016/S0378-1127(99)00207-8</t>
+        </is>
+      </c>
+      <c r="C454" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -5884,8 +7248,11 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1093/forestry/54.2.157</t>
-        </is>
+          <t>https://doi.org/10.1016/j.jhydrol.2007.02.018</t>
+        </is>
+      </c>
+      <c r="C455" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -5896,8 +7263,11 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1006463107</t>
-        </is>
+          <t>https://doi.org/10.1093/forestry/54.2.157</t>
+        </is>
+      </c>
+      <c r="C456" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="457">
@@ -5908,8 +7278,11 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1023/A:1026563926187</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.1006463107</t>
+        </is>
+      </c>
+      <c r="C457" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -5920,8 +7293,11 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1890/07-1739.1</t>
-        </is>
+          <t>https://doi.org/10.1023/A:1026563926187</t>
+        </is>
+      </c>
+      <c r="C458" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="459">
@@ -5932,8 +7308,11 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.biombioe.2011.08.005</t>
-        </is>
+          <t>https://doi.org/10.1890/07-1739.1</t>
+        </is>
+      </c>
+      <c r="C459" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="460">
@@ -5944,8 +7323,11 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/nph.13521</t>
-        </is>
+          <t>https://doi.org/10.1016/j.biombioe.2011.08.005</t>
+        </is>
+      </c>
+      <c r="C460" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -5956,8 +7338,11 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.0403588101</t>
-        </is>
+          <t>https://doi.org/10.1111/nph.13521</t>
+        </is>
+      </c>
+      <c r="C461" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -5968,8 +7353,11 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/jame.20026</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.0403588101</t>
+        </is>
+      </c>
+      <c r="C462" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -5980,8 +7368,11 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/2016MS000686</t>
-        </is>
+          <t>https://doi.org/10.1002/jame.20026</t>
+        </is>
+      </c>
+      <c r="C463" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -5992,8 +7383,11 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1890/14-2098.1</t>
-        </is>
+          <t>https://doi.org/10.1002/2016MS000686</t>
+        </is>
+      </c>
+      <c r="C464" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -6004,8 +7398,11 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.rse.2009.08.010</t>
-        </is>
+          <t>https://doi.org/10.1890/14-2098.1</t>
+        </is>
+      </c>
+      <c r="C465" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="466">
@@ -6016,8 +7413,11 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/2016EF000472</t>
-        </is>
+          <t>https://doi.org/10.1016/j.rse.2009.08.010</t>
+        </is>
+      </c>
+      <c r="C466" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="467">
@@ -6028,8 +7428,11 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41558-019-0545-2</t>
-        </is>
+          <t>https://doi.org/10.1002/2016EF000472</t>
+        </is>
+      </c>
+      <c r="C467" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="468">
@@ -6040,8 +7443,11 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2006GB002868</t>
-        </is>
+          <t>https://doi.org/10.1038/s41558-019-0545-2</t>
+        </is>
+      </c>
+      <c r="C468" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="469">
@@ -6052,8 +7458,11 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s10533-009-9382-0</t>
-        </is>
+          <t>https://doi.org/10.1029/2006GB002868</t>
+        </is>
+      </c>
+      <c r="C469" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -6064,8 +7473,11 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1371/journal.pone.0092942</t>
-        </is>
+          <t>https://doi.org/10.1007/s10533-009-9382-0</t>
+        </is>
+      </c>
+      <c r="C470" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -6076,8 +7488,11 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1086/283931</t>
-        </is>
+          <t>https://doi.org/10.1371/journal.pone.0092942</t>
+        </is>
+      </c>
+      <c r="C471" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -6088,8 +7503,11 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/BF00002772</t>
-        </is>
+          <t>https://doi.org/10.1086/283931</t>
+        </is>
+      </c>
+      <c r="C472" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -6100,8 +7518,11 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1890/08-0127.1</t>
-        </is>
+          <t>https://doi.org/10.1007/BF00002772</t>
+        </is>
+      </c>
+      <c r="C473" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -6112,8 +7533,11 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/0016-7061(76)90066-5</t>
-        </is>
+          <t>https://doi.org/10.1890/08-0127.1</t>
+        </is>
+      </c>
+      <c r="C474" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -6124,8 +7548,11 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.rse.2018.11.016</t>
-        </is>
+          <t>https://doi.org/10.1016/0016-7061(76)90066-5</t>
+        </is>
+      </c>
+      <c r="C475" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="476">
@@ -6136,8 +7563,11 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/ngeo2413</t>
-        </is>
+          <t>https://doi.org/10.1016/j.rse.2018.11.016</t>
+        </is>
+      </c>
+      <c r="C476" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -6148,8 +7578,11 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.scitotenv.2019.136201</t>
-        </is>
+          <t>https://doi.org/10.1016/j.scitotenv.2019.136201</t>
+        </is>
+      </c>
+      <c r="C477" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -6160,8 +7593,11 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/S1002-0160(07)60093-9</t>
-        </is>
+          <t>https://doi.org/10.1016/S1002-0160(07)60093-9</t>
+        </is>
+      </c>
+      <c r="C478" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="479">
@@ -6172,8 +7608,11 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2004GB002296</t>
-        </is>
+          <t>https://doi.org/10.1029/2004GB002296</t>
+        </is>
+      </c>
+      <c r="C479" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -6184,8 +7623,11 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/1365-2435.12979</t>
-        </is>
+          <t>https://doi.org/10.1111/1365-2435.12979</t>
+        </is>
+      </c>
+      <c r="C480" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -6196,8 +7638,11 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-18-713-2026</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-18-713-2026</t>
+        </is>
+      </c>
+      <c r="C481" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -6208,8 +7653,11 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18197534</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.18197534</t>
+        </is>
+      </c>
+      <c r="C482" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -6220,8 +7668,11 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.18392042</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.18392043</t>
+        </is>
+      </c>
+      <c r="C483" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -6232,8 +7683,11 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
-        </is>
+          <t>https://digital-strategy.ec.europa.eu/en/news/new-eu-rules-make-high-value-datasets-available-fuel-artificial-intelligence-and-data-driven</t>
+        </is>
+      </c>
+      <c r="C484" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="485">
@@ -6247,6 +7701,9 @@
           <t>https://www.ecad.eu</t>
         </is>
       </c>
+      <c r="C485" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -6256,8 +7713,11 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://www.github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
-        </is>
+          <t>https://github.com/ecmwf/rodeo-ai-static-datasets/tree/main/seeps4all</t>
+        </is>
+      </c>
+      <c r="C486" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="487">
@@ -6268,8 +7728,11 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arXiv.2412.15687</t>
-        </is>
+          <t>https://doi.org/10.48550/arXiv.2412.15687</t>
+        </is>
+      </c>
+      <c r="C487" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -6280,8 +7743,11 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/qj.3293</t>
-        </is>
+          <t>https://doi.org/10.1002/qj.3293</t>
+        </is>
+      </c>
+      <c r="C488" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="489">
@@ -6292,8 +7758,11 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/MWR-D-19-0323.1</t>
-        </is>
+          <t>https://doi.org/10.1175/MWR-D-19-0323.1</t>
+        </is>
+      </c>
+      <c r="C489" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="490">
@@ -6304,8 +7773,11 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/BAMS-D-23-0162.1</t>
-        </is>
+          <t>https://doi.org/10.1175/BAMS-D-23-0162.1</t>
+        </is>
+      </c>
+      <c r="C490" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="491">
@@ -6316,8 +7788,11 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/1520-0493(1950)078</t>
-        </is>
+          <t>https://doi.org/10.1175/1520-0493(1950)078</t>
+        </is>
+      </c>
+      <c r="C491" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="492">
@@ -6328,8 +7803,11 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-15-2635-2023</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-15-2635-2023</t>
+        </is>
+      </c>
+      <c r="C492" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="493">
@@ -6340,8 +7818,11 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1175/AIES-D-21-0002.1</t>
-        </is>
+          <t>https://doi.org/10.1175/AIES-D-21-0002.1</t>
+        </is>
+      </c>
+      <c r="C493" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -6352,8 +7833,11 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1256/qj.06.25</t>
-        </is>
+          <t>https://doi.org/10.1256/qj.06.25</t>
+        </is>
+      </c>
+      <c r="C494" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="495">
@@ -6364,8 +7848,11 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arXiv.2409.09371</t>
-        </is>
+          <t>https://doi.org/10.48550/arXiv.2409.09371</t>
+        </is>
+      </c>
+      <c r="C495" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="496">
@@ -6376,8 +7863,11 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/joc.773</t>
-        </is>
+          <t>https://doi.org/10.1002/joc.773</t>
+        </is>
+      </c>
+      <c r="C496" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -6388,8 +7878,11 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arxiv.2406.01465</t>
-        </is>
+          <t>https://doi.org/10.48550/arxiv.2406.01465</t>
+        </is>
+      </c>
+      <c r="C497" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -6400,8 +7893,11 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arxiv.2407.15586</t>
-        </is>
+          <t>https://doi.org/10.48550/arxiv.2407.15586</t>
+        </is>
+      </c>
+      <c r="C498" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="499">
@@ -6412,8 +7908,11 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/met.1405</t>
-        </is>
+          <t>https://doi.org/10.1002/met.1405</t>
+        </is>
+      </c>
+      <c r="C499" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -6424,8 +7923,11 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2023MS004019</t>
-        </is>
+          <t>https://doi.org/10.1029/2023MS004019</t>
+        </is>
+      </c>
+      <c r="C500" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="501">
@@ -6436,8 +7938,11 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/qj.656</t>
-        </is>
+          <t>https://doi.org/10.1002/qj.656</t>
+        </is>
+      </c>
+      <c r="C501" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="502">
@@ -6448,8 +7953,11 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arxiv.2501.05648</t>
-        </is>
+          <t>https://doi.org/10.48550/arxiv.2501.05648</t>
+        </is>
+      </c>
+      <c r="C502" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="503">
@@ -6460,8 +7968,11 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/joc.906</t>
-        </is>
+          <t>https://doi.org/10.1002/joc.906</t>
+        </is>
+      </c>
+      <c r="C503" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="504">
@@ -6472,8 +7983,11 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/C2017-0-03921-6</t>
-        </is>
+          <t>https://doi.org/10.1016/C2017-0-03921-6</t>
+        </is>
+      </c>
+      <c r="C504" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="505">
@@ -6484,8 +7998,11 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.48550/arxiv.2302.10493</t>
-        </is>
+          <t>https://doi.org/10.48550/arxiv.2302.10493</t>
+        </is>
+      </c>
+      <c r="C505" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="506">
@@ -6496,8 +8013,11 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-17-7359-2025</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-17-7359-2025</t>
+        </is>
+      </c>
+      <c r="C506" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="507">
@@ -6508,8 +8028,11 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.63xsj3vd4</t>
-        </is>
+          <t>https://doi.org/10.5061/dryad.63xsj3vd4</t>
+        </is>
+      </c>
+      <c r="C507" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -6520,8 +8043,11 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://www.data-nifc.opendata.arcgis.com/</t>
-        </is>
+          <t>https://data-nifc.opendata.arcgis.com/</t>
+        </is>
+      </c>
+      <c r="C508" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="509">
@@ -6535,6 +8061,9 @@
           <t>https://www.mtbs.gov/</t>
         </is>
       </c>
+      <c r="C509" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -6544,8 +8073,11 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.2737/RDS-2013-0009.6</t>
-        </is>
+          <t>https://doi.org/10.2737/RDS-2013-0009.6</t>
+        </is>
+      </c>
+      <c r="C510" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="511">
@@ -6559,6 +8091,9 @@
           <t>https://www.wildfire.gov/page/zip-files</t>
         </is>
       </c>
+      <c r="C511" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -6571,6 +8106,9 @@
           <t>https://www.fire.ca.gov/what-we-do/fire-resource-assessment-program/fire-perimeters</t>
         </is>
       </c>
+      <c r="C512" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -6580,8 +8118,11 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://www.data-nifc.opendata.arcgis.com/datasets/nifc::wfigs-interagency-fire-perimeters/about</t>
-        </is>
+          <t>https://data-nifc.opendata.arcgis.com/datasets/nifc::wfigs-interagency-fire-perimeters/about</t>
+        </is>
+      </c>
+      <c r="C513" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -6595,6 +8136,9 @@
           <t>https://www.sciencebase.gov/catalog/item/61aa537dd34eb622f699df81</t>
         </is>
       </c>
+      <c r="C514" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -6604,8 +8148,11 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://www.data-nifc.opendata.arcgis.com/datasets/nifc::interagencyfireperimeterhistory-all-years-view/about</t>
-        </is>
+          <t>https://data-nifc.opendata.arcgis.com/datasets/nifc::interagencyfireperimeterhistory-all-years-view/about</t>
+        </is>
+      </c>
+      <c r="C515" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="516">
@@ -6616,8 +8163,11 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5281/zenodo.17298252</t>
-        </is>
+          <t>https://doi.org/10.5281/zenodo.17298252</t>
+        </is>
+      </c>
+      <c r="C516" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -6628,8 +8178,11 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s43247-021-00299-0</t>
-        </is>
+          <t>https://doi.org/10.1038/s43247-021-00299-0</t>
+        </is>
+      </c>
+      <c r="C517" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="518">
@@ -6640,8 +8193,11 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/rs12213498</t>
-        </is>
+          <t>https://doi.org/10.3390/rs12213498</t>
+        </is>
+      </c>
+      <c r="C518" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="519">
@@ -6652,8 +8208,11 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/env.2280</t>
-        </is>
+          <t>https://doi.org/10.1002/env.2280</t>
+        </is>
+      </c>
+      <c r="C519" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="520">
@@ -6664,8 +8223,11 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-022-01343-0</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-022-01343-0</t>
+        </is>
+      </c>
+      <c r="C520" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="521">
@@ -6676,8 +8238,11 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/ecs2.2809</t>
-        </is>
+          <t>https://doi.org/10.1002/ecs2.2809</t>
+        </is>
+      </c>
+      <c r="C521" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="522">
@@ -6688,8 +8253,11 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.4996/fireecology.0301003</t>
-        </is>
+          <t>https://doi.org/10.4996/fireecology.0301003</t>
+        </is>
+      </c>
+      <c r="C522" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="523">
@@ -6700,8 +8268,11 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/bg-13-3359-2016</t>
-        </is>
+          <t>https://doi.org/10.5194/bg-13-3359-2016</t>
+        </is>
+      </c>
+      <c r="C523" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -6712,8 +8283,11 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1016/j.rse.2017.06.027</t>
-        </is>
+          <t>https://doi.org/10.1016/j.rse.2017.06.027</t>
+        </is>
+      </c>
+      <c r="C524" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -6724,8 +8298,11 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-16-3061-2024</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-16-3061-2024</t>
+        </is>
+      </c>
+      <c r="C525" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="526">
@@ -6736,8 +8313,11 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41598-019-39284-1</t>
-        </is>
+          <t>https://doi.org/10.1038/s41598-019-39284-1</t>
+        </is>
+      </c>
+      <c r="C526" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="527">
@@ -6748,8 +8328,11 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2024EF005744</t>
-        </is>
+          <t>https://doi.org/10.1029/2024EF005744</t>
+        </is>
+      </c>
+      <c r="C527" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="528">
@@ -6760,8 +8343,11 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5061/dryad.sf7m0cg72</t>
-        </is>
+          <t>https://doi.org/10.5061/dryad.sf7m0cg72</t>
+        </is>
+      </c>
+      <c r="C528" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="529">
@@ -6772,8 +8358,11 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1029/2021GL097131</t>
-        </is>
+          <t>https://doi.org/10.1029/2021GL097131</t>
+        </is>
+      </c>
+      <c r="C529" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -6784,8 +8373,11 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/geosciences6030037</t>
-        </is>
+          <t>https://doi.org/10.3390/geosciences6030037</t>
+        </is>
+      </c>
+      <c r="C530" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -6796,8 +8388,11 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/fee.2190</t>
-        </is>
+          <t>https://doi.org/10.1002/fee.2190</t>
+        </is>
+      </c>
+      <c r="C531" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -6808,8 +8403,11 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/rs13214295</t>
-        </is>
+          <t>https://doi.org/10.3390/rs13214295</t>
+        </is>
+      </c>
+      <c r="C532" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -6820,8 +8418,11 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1002/eap.1420</t>
-        </is>
+          <t>https://doi.org/10.1002/eap.1420</t>
+        </is>
+      </c>
+      <c r="C533" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="534">
@@ -6832,8 +8433,11 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1088/1748-9326/11/3/035002</t>
-        </is>
+          <t>https://doi.org/10.1088/1748-9326/11/3/035002</t>
+        </is>
+      </c>
+      <c r="C534" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -6844,8 +8448,11 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1111/ecog.03378</t>
-        </is>
+          <t>https://doi.org/10.1111/ecog.03378</t>
+        </is>
+      </c>
+      <c r="C535" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -6856,8 +8463,11 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.3390/rs11141735</t>
-        </is>
+          <t>https://doi.org/10.3390/rs11141735</t>
+        </is>
+      </c>
+      <c r="C536" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="537">
@@ -6868,8 +8478,11 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.14358/PERS.74.11.1379</t>
-        </is>
+          <t>https://doi.org/10.14358/PERS.74.11.1379</t>
+        </is>
+      </c>
+      <c r="C537" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -6880,8 +8493,11 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5194/essd-6-1-2014</t>
-        </is>
+          <t>https://doi.org/10.5194/essd-6-1-2014</t>
+        </is>
+      </c>
+      <c r="C538" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="539">
@@ -6892,8 +8508,11 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1038/s41597-023-01955-0</t>
-        </is>
+          <t>https://doi.org/10.1038/s41597-023-01955-0</t>
+        </is>
+      </c>
+      <c r="C539" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -6904,8 +8523,11 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5066/P94UXNTS</t>
-        </is>
+          <t>https://doi.org/10.5066/P94UXNTS</t>
+        </is>
+      </c>
+      <c r="C540" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="541">
@@ -6916,8 +8538,11 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.5066/P9ZXGFY3</t>
-        </is>
+          <t>https://doi.org/10.5066/P9ZXGFY3</t>
+        </is>
+      </c>
+      <c r="C541" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="542">
@@ -6931,6 +8556,9 @@
           <t>https://www.energy.ca.gov/sites/default/files/2019-11/Projections_CCCA4-CEC-2018-014_ADA.pdf</t>
         </is>
       </c>
+      <c r="C542" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -6940,8 +8568,11 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.1110199108</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.1110199108</t>
+        </is>
+      </c>
+      <c r="C543" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="544">
@@ -6952,8 +8583,11 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1007/s40641-016-0031-0</t>
-        </is>
+          <t>https://doi.org/10.1007/s40641-016-0031-0</t>
+        </is>
+      </c>
+      <c r="C544" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="545">
@@ -6964,8 +8598,11 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://www.doi.org/10.1073/pnas.2114069119</t>
-        </is>
+          <t>https://doi.org/10.1073/pnas.2114069119</t>
+        </is>
+      </c>
+      <c r="C545" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
